--- a/GSD/Water Samples/LaJara_LISST_GSD_Spring2023.xlsx
+++ b/GSD/Water Samples/LaJara_LISST_GSD_Spring2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\La_Jara\GSD\Water Samples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\La_Jara\GSD\Water Samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC84C11-3F38-432A-A36E-A2C0523A5398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE008DDA-65BA-4EBD-BFFE-267975423DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{99C89BF0-5701-4EDE-976A-2DC8AC06B2E1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99C89BF0-5701-4EDE-976A-2DC8AC06B2E1}"/>
   </bookViews>
   <sheets>
     <sheet name="ISCO 1 (down)" sheetId="1" r:id="rId1"/>
@@ -1601,7 +1601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1680,13 +1680,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1749,12 +1743,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1767,11 +1756,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2204,6 +2197,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2211,7 +2205,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3008,6 +3001,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3015,7 +3009,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3680,6 +3673,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3687,7 +3681,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5806,43 +5799,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC4F41F3-2406-4DBC-AD18-012969672032}">
   <dimension ref="A2:P152"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="1"/>
-    <col min="7" max="7" width="13.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="29"/>
+    <col min="1" max="1" width="10.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="13.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" customWidth="1"/>
+    <col min="16" max="16" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="52" t="s">
+    <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="I2" s="51" t="s">
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="I2" s="54" t="s">
         <v>336</v>
       </c>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="23"/>
       <c r="B3" s="24"/>
       <c r="C3" s="16" t="s">
@@ -5877,11 +5870,11 @@
       <c r="O3" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="P3" s="30" t="s">
+      <c r="P3" s="28" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>108</v>
       </c>
@@ -5903,32 +5896,32 @@
       <c r="G4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="I4" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="30">
         <v>45033.6875</v>
       </c>
-      <c r="K4" s="31">
-        <v>0</v>
-      </c>
-      <c r="L4" s="34">
+      <c r="K4" s="29">
+        <v>0</v>
+      </c>
+      <c r="L4" s="32">
         <v>94.166666666666671</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="29">
         <v>106.21</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="33">
         <v>74.67</v>
       </c>
-      <c r="O4" s="47">
+      <c r="O4" s="45">
         <v>205</v>
       </c>
-      <c r="P4" s="33" t="s">
+      <c r="P4" s="31" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>124</v>
       </c>
@@ -5950,33 +5943,33 @@
       <c r="G5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I5" s="31" t="s">
+      <c r="I5" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="J5" s="32">
+      <c r="J5" s="30">
         <v>45033.854166666664</v>
       </c>
-      <c r="K5" s="31">
-        <v>0</v>
-      </c>
-      <c r="L5" s="34">
+      <c r="K5" s="29">
+        <v>0</v>
+      </c>
+      <c r="L5" s="32">
         <v>95.537499999999994</v>
       </c>
-      <c r="M5" s="39">
+      <c r="M5" s="37">
         <v>51.232500000000002</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="38">
         <v>45.327500000000001</v>
       </c>
-      <c r="O5" s="31">
+      <c r="O5" s="29">
         <f t="shared" ref="O5" si="0">O4+1</f>
         <v>206</v>
       </c>
-      <c r="P5" s="33" t="s">
+      <c r="P5" s="31" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>131</v>
       </c>
@@ -5998,98 +5991,98 @@
       <c r="G6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="I6" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="30">
         <v>45034.020833333336</v>
       </c>
-      <c r="K6" s="31">
-        <v>0</v>
-      </c>
-      <c r="L6" s="31">
+      <c r="K6" s="29">
+        <v>0</v>
+      </c>
+      <c r="L6" s="29">
         <v>97</v>
       </c>
-      <c r="M6" s="31">
+      <c r="M6" s="29">
         <v>59.16</v>
       </c>
-      <c r="N6" s="35">
+      <c r="N6" s="33">
         <v>68.435000000000002</v>
       </c>
-      <c r="O6" s="47">
+      <c r="O6" s="45">
         <v>222</v>
       </c>
-      <c r="P6" s="33" t="s">
+      <c r="P6" s="31" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="30">
         <v>45034</v>
       </c>
-      <c r="C7" s="31">
-        <v>0</v>
-      </c>
-      <c r="D7" s="31">
+      <c r="C7" s="29">
+        <v>0</v>
+      </c>
+      <c r="D7" s="29">
         <v>97</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="29">
         <v>40.4</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="29">
         <v>56.48</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="I7" s="31" t="s">
+      <c r="I7" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="J7" s="32">
+      <c r="J7" s="30">
         <v>45034.1875</v>
       </c>
-      <c r="K7" s="31">
-        <v>0</v>
-      </c>
-      <c r="L7" s="31">
+      <c r="K7" s="29">
+        <v>0</v>
+      </c>
+      <c r="L7" s="29">
         <v>96.95</v>
       </c>
-      <c r="M7" s="34">
+      <c r="M7" s="32">
         <v>48.467500000000001</v>
       </c>
-      <c r="N7" s="37">
+      <c r="N7" s="35">
         <v>66.542500000000004</v>
       </c>
-      <c r="O7" s="47">
+      <c r="O7" s="45">
         <v>207</v>
       </c>
-      <c r="P7" s="33" t="s">
+      <c r="P7" s="31" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="30">
         <v>45034</v>
       </c>
-      <c r="C8" s="31">
-        <v>0</v>
-      </c>
-      <c r="D8" s="31">
+      <c r="C8" s="29">
+        <v>0</v>
+      </c>
+      <c r="D8" s="29">
         <v>97</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="29">
         <v>45.64</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="29">
         <v>62.36</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="29" t="s">
         <v>176</v>
       </c>
       <c r="I8" s="2" t="s">
@@ -6113,30 +6106,30 @@
       <c r="O8" s="5">
         <v>223</v>
       </c>
-      <c r="P8" s="29" t="s">
+      <c r="P8" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="30">
         <v>45034</v>
       </c>
-      <c r="C9" s="31">
-        <v>0</v>
-      </c>
-      <c r="D9" s="31">
+      <c r="C9" s="29">
+        <v>0</v>
+      </c>
+      <c r="D9" s="29">
         <v>97</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="29">
         <v>49.2</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="29">
         <v>67.64</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="29" t="s">
         <v>178</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -6161,107 +6154,107 @@
         <f t="shared" ref="O9:O20" si="1">O8+1</f>
         <v>224</v>
       </c>
-      <c r="P9" s="29" t="s">
+      <c r="P9" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="B10" s="38">
+      <c r="B10" s="36">
         <v>45033</v>
       </c>
-      <c r="C10" s="31">
-        <v>0</v>
-      </c>
-      <c r="D10" s="31">
+      <c r="C10" s="29">
+        <v>0</v>
+      </c>
+      <c r="D10" s="29">
         <v>95.5</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="29">
         <v>50.12</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="29">
         <v>43.74</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="I10" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="J10" s="36">
+      <c r="J10" s="34">
         <v>45034.6875</v>
       </c>
-      <c r="K10" s="31">
-        <v>0</v>
-      </c>
-      <c r="L10" s="31">
+      <c r="K10" s="29">
+        <v>0</v>
+      </c>
+      <c r="L10" s="29">
         <v>92.174999999999997</v>
       </c>
-      <c r="M10" s="31">
+      <c r="M10" s="29">
         <v>78.710000000000008</v>
       </c>
-      <c r="N10" s="35">
+      <c r="N10" s="33">
         <v>47.094999999999999</v>
       </c>
-      <c r="O10" s="31">
+      <c r="O10" s="29">
         <f t="shared" si="1"/>
         <v>225</v>
       </c>
-      <c r="P10" s="33" t="s">
+      <c r="P10" s="31" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="30">
         <v>45033</v>
       </c>
-      <c r="C11" s="31">
-        <v>0</v>
-      </c>
-      <c r="D11" s="31">
+      <c r="C11" s="29">
+        <v>0</v>
+      </c>
+      <c r="D11" s="29">
         <v>94.2</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="29">
         <v>106.35</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="29">
         <v>74.72</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="I11" s="31" t="s">
+      <c r="I11" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="J11" s="36">
+      <c r="J11" s="34">
         <v>45034.895833333336</v>
       </c>
-      <c r="K11" s="31">
-        <v>0</v>
-      </c>
-      <c r="L11" s="31">
+      <c r="K11" s="29">
+        <v>0</v>
+      </c>
+      <c r="L11" s="29">
         <v>97</v>
       </c>
-      <c r="M11" s="31">
+      <c r="M11" s="29">
         <v>45.419999999999995</v>
       </c>
-      <c r="N11" s="37">
+      <c r="N11" s="35">
         <v>78.826666666666668</v>
       </c>
-      <c r="O11" s="31">
+      <c r="O11" s="29">
         <f t="shared" si="1"/>
         <v>226</v>
       </c>
-      <c r="P11" s="33" t="s">
+      <c r="P11" s="31" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>127</v>
       </c>
@@ -6283,52 +6276,52 @@
       <c r="G12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I12" s="31" t="s">
+      <c r="I12" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="J12" s="36">
+      <c r="J12" s="34">
         <v>45035.104166666664</v>
       </c>
-      <c r="K12" s="31">
-        <v>0</v>
-      </c>
-      <c r="L12" s="31">
+      <c r="K12" s="29">
+        <v>0</v>
+      </c>
+      <c r="L12" s="29">
         <v>95.074999999999989</v>
       </c>
-      <c r="M12" s="34">
+      <c r="M12" s="32">
         <v>74.752499999999998</v>
       </c>
-      <c r="N12" s="37">
+      <c r="N12" s="35">
         <v>68.867500000000007</v>
       </c>
-      <c r="O12" s="31">
+      <c r="O12" s="29">
         <f t="shared" si="1"/>
         <v>227</v>
       </c>
-      <c r="P12" s="33" t="s">
+      <c r="P12" s="31" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="30">
         <v>45033</v>
       </c>
-      <c r="C13" s="31">
-        <v>0</v>
-      </c>
-      <c r="D13" s="31">
+      <c r="C13" s="29">
+        <v>0</v>
+      </c>
+      <c r="D13" s="29">
         <v>95.4</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="29">
         <v>50.4</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="29">
         <v>44.83</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="29" t="s">
         <v>191</v>
       </c>
       <c r="H13" t="s">
@@ -6356,11 +6349,11 @@
         <f t="shared" si="1"/>
         <v>228</v>
       </c>
-      <c r="P13" s="29" t="s">
+      <c r="P13" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>120</v>
       </c>
@@ -6382,33 +6375,33 @@
       <c r="G14" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I14" s="31" t="s">
+      <c r="I14" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="J14" s="32">
+      <c r="J14" s="30">
         <v>45035.520833333336</v>
       </c>
-      <c r="K14" s="31">
-        <v>0</v>
-      </c>
-      <c r="L14" s="31">
+      <c r="K14" s="29">
+        <v>0</v>
+      </c>
+      <c r="L14" s="29">
         <v>95.75</v>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="29">
         <v>56.59</v>
       </c>
-      <c r="N14" s="35">
+      <c r="N14" s="33">
         <v>57.344999999999999</v>
       </c>
-      <c r="O14" s="31">
+      <c r="O14" s="29">
         <f t="shared" si="1"/>
         <v>229</v>
       </c>
-      <c r="P14" s="33" t="s">
+      <c r="P14" s="31" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>92</v>
       </c>
@@ -6452,30 +6445,30 @@
         <f t="shared" si="1"/>
         <v>230</v>
       </c>
-      <c r="P15" s="29" t="s">
+      <c r="P15" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="30">
         <v>45033</v>
       </c>
-      <c r="C16" s="31">
-        <v>0</v>
-      </c>
-      <c r="D16" s="31">
+      <c r="C16" s="29">
+        <v>0</v>
+      </c>
+      <c r="D16" s="29">
         <v>95.55</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="29">
         <v>53.47</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="29">
         <v>46.82</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="29" t="s">
         <v>195</v>
       </c>
       <c r="I16" s="2" t="s">
@@ -6500,11 +6493,11 @@
         <f t="shared" si="1"/>
         <v>231</v>
       </c>
-      <c r="P16" s="29" t="s">
+      <c r="P16" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>117</v>
       </c>
@@ -6548,30 +6541,30 @@
         <f t="shared" si="1"/>
         <v>232</v>
       </c>
-      <c r="P17" s="29" t="s">
+      <c r="P17" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="30">
         <v>45033</v>
       </c>
-      <c r="C18" s="31">
-        <v>0</v>
-      </c>
-      <c r="D18" s="31">
+      <c r="C18" s="29">
+        <v>0</v>
+      </c>
+      <c r="D18" s="29">
         <v>94.2</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="29">
         <v>101.59</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="29">
         <v>71.680000000000007</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="29" t="s">
         <v>198</v>
       </c>
       <c r="I18" s="2" t="s">
@@ -6596,11 +6589,11 @@
         <f t="shared" si="1"/>
         <v>233</v>
       </c>
-      <c r="P18" s="29" t="s">
+      <c r="P18" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>127</v>
       </c>
@@ -6622,33 +6615,33 @@
       <c r="G19" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I19" s="31" t="s">
+      <c r="I19" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="J19" s="36">
+      <c r="J19" s="34">
         <v>45037.395833333336</v>
       </c>
-      <c r="K19" s="31">
-        <v>0</v>
-      </c>
-      <c r="L19" s="39">
+      <c r="K19" s="29">
+        <v>0</v>
+      </c>
+      <c r="L19" s="37">
         <v>97.166666666666671</v>
       </c>
-      <c r="M19" s="39">
+      <c r="M19" s="37">
         <v>27.229999999999997</v>
       </c>
-      <c r="N19" s="40">
+      <c r="N19" s="38">
         <v>49.800000000000004</v>
       </c>
-      <c r="O19" s="31">
+      <c r="O19" s="29">
         <f t="shared" si="1"/>
         <v>234</v>
       </c>
-      <c r="P19" s="33" t="s">
+      <c r="P19" s="31" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>114</v>
       </c>
@@ -6692,11 +6685,11 @@
         <f t="shared" si="1"/>
         <v>235</v>
       </c>
-      <c r="P20" s="29" t="s">
+      <c r="P20" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>134</v>
       </c>
@@ -6739,11 +6732,11 @@
       <c r="O21" s="5">
         <v>254</v>
       </c>
-      <c r="P21" s="29" t="s">
+      <c r="P21" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>119</v>
       </c>
@@ -6787,11 +6780,11 @@
         <f t="shared" ref="O22:O35" si="2">O21+1</f>
         <v>255</v>
       </c>
-      <c r="P22" s="29" t="s">
+      <c r="P22" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>135</v>
       </c>
@@ -6835,11 +6828,11 @@
         <f t="shared" si="2"/>
         <v>256</v>
       </c>
-      <c r="P23" s="29" t="s">
+      <c r="P23" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>96</v>
       </c>
@@ -6883,30 +6876,30 @@
         <f t="shared" si="2"/>
         <v>257</v>
       </c>
-      <c r="P24" s="29" t="s">
+      <c r="P24" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="31" t="s">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="38">
+      <c r="B25" s="36">
         <v>45034</v>
       </c>
-      <c r="C25" s="31">
-        <v>0</v>
-      </c>
-      <c r="D25" s="31">
+      <c r="C25" s="29">
+        <v>0</v>
+      </c>
+      <c r="D25" s="29">
         <v>97.1</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="29">
         <v>51.48</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="29">
         <v>62.56</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="29" t="s">
         <v>181</v>
       </c>
       <c r="I25" s="2" t="s">
@@ -6931,30 +6924,30 @@
         <f t="shared" si="2"/>
         <v>258</v>
       </c>
-      <c r="P25" s="29" t="s">
+      <c r="P25" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="30">
         <v>45033</v>
       </c>
-      <c r="C26" s="31">
-        <v>0</v>
-      </c>
-      <c r="D26" s="31">
+      <c r="C26" s="29">
+        <v>0</v>
+      </c>
+      <c r="D26" s="29">
         <v>95.7</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="29">
         <v>50.94</v>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="29">
         <v>45.92</v>
       </c>
-      <c r="G26" s="31" t="s">
+      <c r="G26" s="29" t="s">
         <v>197</v>
       </c>
       <c r="I26" s="2" t="s">
@@ -6979,30 +6972,30 @@
         <f t="shared" si="2"/>
         <v>259</v>
       </c>
-      <c r="P26" s="29" t="s">
+      <c r="P26" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="31" t="s">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="30">
         <v>45033</v>
       </c>
-      <c r="C27" s="31">
-        <v>0</v>
-      </c>
-      <c r="D27" s="31">
+      <c r="C27" s="29">
+        <v>0</v>
+      </c>
+      <c r="D27" s="29">
         <v>94.1</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="29">
         <v>110.69</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="29">
         <v>77.61</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="G27" s="29" t="s">
         <v>202</v>
       </c>
       <c r="I27" s="2" t="s">
@@ -7027,30 +7020,30 @@
         <f t="shared" si="2"/>
         <v>260</v>
       </c>
-      <c r="P27" s="29" t="s">
+      <c r="P27" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="30">
         <v>45035</v>
       </c>
-      <c r="C28" s="31">
-        <v>0</v>
-      </c>
-      <c r="D28" s="31">
+      <c r="C28" s="29">
+        <v>0</v>
+      </c>
+      <c r="D28" s="29">
         <v>95.8</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="29">
         <v>52.71</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="29">
         <v>55.5</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="29" t="s">
         <v>219</v>
       </c>
       <c r="I28" s="2" t="s">
@@ -7075,11 +7068,11 @@
         <f t="shared" si="2"/>
         <v>261</v>
       </c>
-      <c r="P28" s="29" t="s">
+      <c r="P28" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>138</v>
       </c>
@@ -7123,11 +7116,11 @@
         <f t="shared" si="2"/>
         <v>262</v>
       </c>
-      <c r="P29" s="29" t="s">
+      <c r="P29" s="1" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>121</v>
       </c>
@@ -7171,30 +7164,30 @@
         <f t="shared" si="2"/>
         <v>263</v>
       </c>
-      <c r="P30" s="29" t="s">
+      <c r="P30" s="1" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="31" t="s">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="30">
         <v>45034</v>
       </c>
-      <c r="C31" s="31">
-        <v>0</v>
-      </c>
-      <c r="D31" s="31">
+      <c r="C31" s="29">
+        <v>0</v>
+      </c>
+      <c r="D31" s="29">
         <v>96.8</v>
       </c>
-      <c r="E31" s="31">
+      <c r="E31" s="29">
         <v>58.63</v>
       </c>
-      <c r="F31" s="31">
+      <c r="F31" s="29">
         <v>79.69</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="G31" s="29" t="s">
         <v>180</v>
       </c>
       <c r="I31" s="2" t="s">
@@ -7219,30 +7212,30 @@
         <f t="shared" si="2"/>
         <v>264</v>
       </c>
-      <c r="P31" s="29" t="s">
+      <c r="P31" s="1" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="31" t="s">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="B32" s="38">
+      <c r="B32" s="36">
         <v>45034</v>
       </c>
-      <c r="C32" s="31">
-        <v>0</v>
-      </c>
-      <c r="D32" s="31">
+      <c r="C32" s="29">
+        <v>0</v>
+      </c>
+      <c r="D32" s="29">
         <v>96.9</v>
       </c>
-      <c r="E32" s="31">
+      <c r="E32" s="29">
         <v>65.17</v>
       </c>
-      <c r="F32" s="31">
+      <c r="F32" s="29">
         <v>73.819999999999993</v>
       </c>
-      <c r="G32" s="31" t="s">
+      <c r="G32" s="29" t="s">
         <v>185</v>
       </c>
       <c r="I32" s="2" t="s">
@@ -7267,30 +7260,30 @@
         <f t="shared" si="2"/>
         <v>265</v>
       </c>
-      <c r="P32" s="29" t="s">
+      <c r="P32" s="1" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="B33" s="32">
+      <c r="B33" s="30">
         <v>45034</v>
       </c>
-      <c r="C33" s="31">
-        <v>0</v>
-      </c>
-      <c r="D33" s="31">
+      <c r="C33" s="29">
+        <v>0</v>
+      </c>
+      <c r="D33" s="29">
         <v>96.9</v>
       </c>
-      <c r="E33" s="31">
+      <c r="E33" s="29">
         <v>65.83</v>
       </c>
-      <c r="F33" s="31">
+      <c r="F33" s="29">
         <v>73.38</v>
       </c>
-      <c r="G33" s="31" t="s">
+      <c r="G33" s="29" t="s">
         <v>187</v>
       </c>
       <c r="I33" s="2" t="s">
@@ -7315,11 +7308,11 @@
         <f t="shared" si="2"/>
         <v>266</v>
       </c>
-      <c r="P33" s="29" t="s">
+      <c r="P33" s="1" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>144</v>
       </c>
@@ -7363,11 +7356,11 @@
         <f t="shared" si="2"/>
         <v>267</v>
       </c>
-      <c r="P34" s="29" t="s">
+      <c r="P34" s="1" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>94</v>
       </c>
@@ -7411,11 +7404,11 @@
         <f t="shared" si="2"/>
         <v>268</v>
       </c>
-      <c r="P35" s="29" t="s">
+      <c r="P35" s="1" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>110</v>
       </c>
@@ -7458,11 +7451,11 @@
       <c r="O36" s="5">
         <v>292</v>
       </c>
-      <c r="P36" s="29" t="s">
+      <c r="P36" s="1" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>96</v>
       </c>
@@ -7505,11 +7498,11 @@
       <c r="O37" s="5">
         <v>293</v>
       </c>
-      <c r="P37" s="29" t="s">
+      <c r="P37" s="1" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>112</v>
       </c>
@@ -7552,11 +7545,11 @@
       <c r="O38" s="2">
         <v>294</v>
       </c>
-      <c r="P38" s="29" t="s">
+      <c r="P38" s="1" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>131</v>
       </c>
@@ -7599,11 +7592,11 @@
       <c r="O39" s="5">
         <v>295</v>
       </c>
-      <c r="P39" s="29" t="s">
+      <c r="P39" s="1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>136</v>
       </c>
@@ -7646,11 +7639,11 @@
       <c r="O40" s="5">
         <v>296</v>
       </c>
-      <c r="P40" s="29" t="s">
+      <c r="P40" s="1" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>143</v>
       </c>
@@ -7693,11 +7686,11 @@
       <c r="O41" s="5">
         <v>297</v>
       </c>
-      <c r="P41" s="29" t="s">
+      <c r="P41" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>91</v>
       </c>
@@ -7740,11 +7733,11 @@
       <c r="O42" s="5">
         <v>298</v>
       </c>
-      <c r="P42" s="29" t="s">
+      <c r="P42" s="1" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>117</v>
       </c>
@@ -7787,30 +7780,30 @@
       <c r="O43" s="5">
         <v>299</v>
       </c>
-      <c r="P43" s="29" t="s">
+      <c r="P43" s="1" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="31" t="s">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="B44" s="38">
+      <c r="B44" s="36">
         <v>45034</v>
       </c>
-      <c r="C44" s="31">
-        <v>0</v>
-      </c>
-      <c r="D44" s="31">
+      <c r="C44" s="29">
+        <v>0</v>
+      </c>
+      <c r="D44" s="29">
         <v>97.1</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="29">
         <v>54.16</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="29">
         <v>63.98</v>
       </c>
-      <c r="G44" s="31" t="s">
+      <c r="G44" s="29" t="s">
         <v>183</v>
       </c>
       <c r="I44" s="2" t="s">
@@ -7834,11 +7827,11 @@
       <c r="O44" s="5">
         <v>300</v>
       </c>
-      <c r="P44" s="29" t="s">
+      <c r="P44" s="1" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>92</v>
       </c>
@@ -7881,11 +7874,11 @@
       <c r="O45" s="5">
         <v>301</v>
       </c>
-      <c r="P45" s="29" t="s">
+      <c r="P45" s="1" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>120</v>
       </c>
@@ -7928,11 +7921,11 @@
       <c r="O46" s="5">
         <v>315</v>
       </c>
-      <c r="P46" s="29" t="s">
+      <c r="P46" s="1" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>129</v>
       </c>
@@ -7975,11 +7968,11 @@
       <c r="O47" s="5">
         <v>316</v>
       </c>
-      <c r="P47" s="29" t="s">
+      <c r="P47" s="1" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>109</v>
       </c>
@@ -8022,11 +8015,11 @@
       <c r="O48" s="5">
         <v>317</v>
       </c>
-      <c r="P48" s="29" t="s">
+      <c r="P48" s="1" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>135</v>
       </c>
@@ -8069,11 +8062,11 @@
       <c r="O49" s="5">
         <v>319</v>
       </c>
-      <c r="P49" s="29" t="s">
+      <c r="P49" s="1" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>108</v>
       </c>
@@ -8116,30 +8109,30 @@
       <c r="O50" s="5">
         <v>320</v>
       </c>
-      <c r="P50" s="29" t="s">
+      <c r="P50" s="1" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="31" t="s">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A51" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="B51" s="32">
+      <c r="B51" s="30">
         <v>45046</v>
       </c>
-      <c r="C51" s="31">
-        <v>0</v>
-      </c>
-      <c r="D51" s="31">
+      <c r="C51" s="29">
+        <v>0</v>
+      </c>
+      <c r="D51" s="29">
         <v>94.8</v>
       </c>
-      <c r="E51" s="31">
+      <c r="E51" s="29">
         <v>63.56</v>
       </c>
-      <c r="F51" s="31">
+      <c r="F51" s="29">
         <v>74.05</v>
       </c>
-      <c r="G51" s="31" t="s">
+      <c r="G51" s="29" t="s">
         <v>137</v>
       </c>
       <c r="I51" s="2" t="s">
@@ -8163,11 +8156,11 @@
       <c r="O51" s="5">
         <v>321</v>
       </c>
-      <c r="P51" s="29" t="s">
+      <c r="P51" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>127</v>
       </c>
@@ -8210,105 +8203,105 @@
       <c r="O52" s="5">
         <v>322</v>
       </c>
-      <c r="P52" s="29" t="s">
+      <c r="P52" s="1" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="31" t="s">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A53" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="B53" s="32">
+      <c r="B53" s="30">
         <v>45046</v>
       </c>
-      <c r="C53" s="31">
-        <v>0</v>
-      </c>
-      <c r="D53" s="31">
+      <c r="C53" s="29">
+        <v>0</v>
+      </c>
+      <c r="D53" s="29">
         <v>94.9</v>
       </c>
-      <c r="E53" s="31">
+      <c r="E53" s="29">
         <v>85.89</v>
       </c>
-      <c r="F53" s="31">
+      <c r="F53" s="29">
         <v>79.16</v>
       </c>
-      <c r="G53" s="31" t="s">
+      <c r="G53" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="I53" s="31" t="s">
+      <c r="I53" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="J53" s="32">
+      <c r="J53" s="30">
         <v>45046.75</v>
       </c>
-      <c r="K53" s="31">
-        <v>0</v>
-      </c>
-      <c r="L53" s="31">
+      <c r="K53" s="29">
+        <v>0</v>
+      </c>
+      <c r="L53" s="29">
         <v>94.8</v>
       </c>
-      <c r="M53" s="31">
+      <c r="M53" s="29">
         <v>63.56</v>
       </c>
-      <c r="N53" s="35">
+      <c r="N53" s="33">
         <v>74.05</v>
       </c>
-      <c r="O53" s="47">
+      <c r="O53" s="45">
         <v>323</v>
       </c>
-      <c r="P53" s="33" t="s">
+      <c r="P53" s="31" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="31" t="s">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A54" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="32">
+      <c r="B54" s="30">
         <v>45047</v>
       </c>
-      <c r="C54" s="31">
-        <v>0</v>
-      </c>
-      <c r="D54" s="31">
+      <c r="C54" s="29">
+        <v>0</v>
+      </c>
+      <c r="D54" s="29">
         <v>97</v>
       </c>
-      <c r="E54" s="31">
+      <c r="E54" s="29">
         <v>44.99</v>
       </c>
-      <c r="F54" s="31">
+      <c r="F54" s="29">
         <v>102.87</v>
       </c>
-      <c r="G54" s="31" t="s">
+      <c r="G54" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="I54" s="31" t="s">
+      <c r="I54" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="J54" s="32">
+      <c r="J54" s="30">
         <v>45046.958333333336</v>
       </c>
-      <c r="K54" s="31">
-        <v>0</v>
-      </c>
-      <c r="L54" s="31">
+      <c r="K54" s="29">
+        <v>0</v>
+      </c>
+      <c r="L54" s="29">
         <v>94.9</v>
       </c>
-      <c r="M54" s="31">
+      <c r="M54" s="29">
         <v>85.89</v>
       </c>
-      <c r="N54" s="35">
+      <c r="N54" s="33">
         <v>79.16</v>
       </c>
-      <c r="O54" s="47">
+      <c r="O54" s="45">
         <v>324</v>
       </c>
-      <c r="P54" s="33" t="s">
+      <c r="P54" s="31" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>134</v>
       </c>
@@ -8351,11 +8344,11 @@
       <c r="O55" s="5">
         <v>325</v>
       </c>
-      <c r="P55" s="29" t="s">
+      <c r="P55" s="1" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>141</v>
       </c>
@@ -8398,201 +8391,201 @@
       <c r="O56" s="5">
         <v>326</v>
       </c>
-      <c r="P56" s="29" t="s">
+      <c r="P56" s="1" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="31" t="s">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A57" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="B57" s="32">
+      <c r="B57" s="30">
         <v>45047</v>
       </c>
-      <c r="C57" s="31">
-        <v>0</v>
-      </c>
-      <c r="D57" s="31">
+      <c r="C57" s="29">
+        <v>0</v>
+      </c>
+      <c r="D57" s="29">
         <v>95.4</v>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="29">
         <v>50.13</v>
       </c>
-      <c r="F57" s="31">
+      <c r="F57" s="29">
         <v>58.66</v>
       </c>
-      <c r="G57" s="31" t="s">
+      <c r="G57" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="I57" s="31" t="s">
+      <c r="I57" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="J57" s="32">
+      <c r="J57" s="30">
         <v>45047.583333333336</v>
       </c>
-      <c r="K57" s="31">
-        <v>0</v>
-      </c>
-      <c r="L57" s="31">
+      <c r="K57" s="29">
+        <v>0</v>
+      </c>
+      <c r="L57" s="29">
         <v>95.4</v>
       </c>
-      <c r="M57" s="31">
+      <c r="M57" s="29">
         <v>50.13</v>
       </c>
-      <c r="N57" s="35">
+      <c r="N57" s="33">
         <v>58.66</v>
       </c>
-      <c r="O57" s="47">
+      <c r="O57" s="45">
         <v>327</v>
       </c>
-      <c r="P57" s="33" t="s">
+      <c r="P57" s="31" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="31" t="s">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A58" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="B58" s="32">
+      <c r="B58" s="30">
         <v>45048</v>
       </c>
-      <c r="C58" s="31">
-        <v>0</v>
-      </c>
-      <c r="D58" s="31">
+      <c r="C58" s="29">
+        <v>0</v>
+      </c>
+      <c r="D58" s="29">
         <v>96.9</v>
       </c>
-      <c r="E58" s="31">
+      <c r="E58" s="29">
         <v>31.62</v>
       </c>
-      <c r="F58" s="31">
+      <c r="F58" s="29">
         <v>76.459999999999994</v>
       </c>
-      <c r="G58" s="31" t="s">
+      <c r="G58" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="I58" s="31" t="s">
+      <c r="I58" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="J58" s="32">
+      <c r="J58" s="30">
         <v>45047.833333333336</v>
       </c>
-      <c r="K58" s="31">
-        <v>0</v>
-      </c>
-      <c r="L58" s="31">
+      <c r="K58" s="29">
+        <v>0</v>
+      </c>
+      <c r="L58" s="29">
         <v>97</v>
       </c>
-      <c r="M58" s="31">
+      <c r="M58" s="29">
         <v>44.99</v>
       </c>
-      <c r="N58" s="35">
+      <c r="N58" s="33">
         <v>102.87</v>
       </c>
-      <c r="O58" s="47">
+      <c r="O58" s="45">
         <v>343</v>
       </c>
-      <c r="P58" s="33" t="s">
+      <c r="P58" s="31" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="31" t="s">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A59" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="B59" s="32">
+      <c r="B59" s="30">
         <v>45048</v>
       </c>
-      <c r="C59" s="31">
-        <v>0</v>
-      </c>
-      <c r="D59" s="31">
+      <c r="C59" s="29">
+        <v>0</v>
+      </c>
+      <c r="D59" s="29">
         <v>96.6</v>
       </c>
-      <c r="E59" s="31">
+      <c r="E59" s="29">
         <v>35.729999999999997</v>
       </c>
-      <c r="F59" s="31">
+      <c r="F59" s="29">
         <v>68.709999999999994</v>
       </c>
-      <c r="G59" s="31" t="s">
+      <c r="G59" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="I59" s="31" t="s">
+      <c r="I59" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="J59" s="32">
+      <c r="J59" s="30">
         <v>45048.125</v>
       </c>
-      <c r="K59" s="31">
-        <v>0</v>
-      </c>
-      <c r="L59" s="31">
+      <c r="K59" s="29">
+        <v>0</v>
+      </c>
+      <c r="L59" s="29">
         <v>96.6</v>
       </c>
-      <c r="M59" s="31">
+      <c r="M59" s="29">
         <v>35.729999999999997</v>
       </c>
-      <c r="N59" s="35">
+      <c r="N59" s="33">
         <v>68.709999999999994</v>
       </c>
-      <c r="O59" s="31">
+      <c r="O59" s="29">
         <f t="shared" ref="O59:O65" si="3">O58+1</f>
         <v>344</v>
       </c>
-      <c r="P59" s="33" t="s">
+      <c r="P59" s="31" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="31" t="s">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A60" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="B60" s="32">
+      <c r="B60" s="30">
         <v>45048</v>
       </c>
-      <c r="C60" s="31">
-        <v>0</v>
-      </c>
-      <c r="D60" s="31">
+      <c r="C60" s="29">
+        <v>0</v>
+      </c>
+      <c r="D60" s="29">
         <v>98</v>
       </c>
-      <c r="E60" s="31">
+      <c r="E60" s="29">
         <v>25.42</v>
       </c>
-      <c r="F60" s="31">
+      <c r="F60" s="29">
         <v>78.58</v>
       </c>
-      <c r="G60" s="31" t="s">
+      <c r="G60" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="I60" s="31" t="s">
+      <c r="I60" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="J60" s="32">
+      <c r="J60" s="30">
         <v>45048.416666666664</v>
       </c>
-      <c r="K60" s="31">
-        <v>0</v>
-      </c>
-      <c r="L60" s="31">
+      <c r="K60" s="29">
+        <v>0</v>
+      </c>
+      <c r="L60" s="29">
         <v>96.9</v>
       </c>
-      <c r="M60" s="31">
+      <c r="M60" s="29">
         <v>31.62</v>
       </c>
-      <c r="N60" s="35">
+      <c r="N60" s="33">
         <v>76.459999999999994</v>
       </c>
-      <c r="O60" s="31">
+      <c r="O60" s="29">
         <f t="shared" si="3"/>
         <v>345</v>
       </c>
-      <c r="P60" s="33" t="s">
+      <c r="P60" s="31" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>91</v>
       </c>
@@ -8614,33 +8607,33 @@
       <c r="G61" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I61" s="31" t="s">
+      <c r="I61" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="J61" s="32">
+      <c r="J61" s="30">
         <v>45048.708333333336</v>
       </c>
-      <c r="K61" s="31">
-        <v>0</v>
-      </c>
-      <c r="L61" s="31">
+      <c r="K61" s="29">
+        <v>0</v>
+      </c>
+      <c r="L61" s="29">
         <v>98</v>
       </c>
-      <c r="M61" s="31">
+      <c r="M61" s="29">
         <v>25.42</v>
       </c>
-      <c r="N61" s="35">
+      <c r="N61" s="33">
         <v>78.58</v>
       </c>
-      <c r="O61" s="31">
+      <c r="O61" s="29">
         <f t="shared" si="3"/>
         <v>346</v>
       </c>
-      <c r="P61" s="33" t="s">
+      <c r="P61" s="31" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>112</v>
       </c>
@@ -8684,11 +8677,11 @@
         <f t="shared" si="3"/>
         <v>347</v>
       </c>
-      <c r="P62" s="29" t="s">
+      <c r="P62" s="1" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>114</v>
       </c>
@@ -8732,30 +8725,30 @@
         <f t="shared" si="3"/>
         <v>348</v>
       </c>
-      <c r="P63" s="29" t="s">
+      <c r="P63" s="1" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="31" t="s">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A64" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="B64" s="32">
+      <c r="B64" s="30">
         <v>45049</v>
       </c>
-      <c r="C64" s="31">
-        <v>0</v>
-      </c>
-      <c r="D64" s="31">
+      <c r="C64" s="29">
+        <v>0</v>
+      </c>
+      <c r="D64" s="29">
         <v>94.6</v>
       </c>
-      <c r="E64" s="31">
+      <c r="E64" s="29">
         <v>68.760000000000005</v>
       </c>
-      <c r="F64" s="31">
+      <c r="F64" s="29">
         <v>86.67</v>
       </c>
-      <c r="G64" s="31" t="s">
+      <c r="G64" s="29" t="s">
         <v>118</v>
       </c>
       <c r="I64" s="2" t="s">
@@ -8780,11 +8773,11 @@
         <f t="shared" si="3"/>
         <v>349</v>
       </c>
-      <c r="P64" s="29" t="s">
+      <c r="P64" s="1" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>119</v>
       </c>
@@ -8806,33 +8799,33 @@
       <c r="G65" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I65" s="31" t="s">
+      <c r="I65" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="J65" s="32">
+      <c r="J65" s="30">
         <v>45049.833333333336</v>
       </c>
-      <c r="K65" s="31">
-        <v>0</v>
-      </c>
-      <c r="L65" s="31">
+      <c r="K65" s="29">
+        <v>0</v>
+      </c>
+      <c r="L65" s="29">
         <v>94.6</v>
       </c>
-      <c r="M65" s="31">
+      <c r="M65" s="29">
         <v>68.760000000000005</v>
       </c>
-      <c r="N65" s="35">
+      <c r="N65" s="33">
         <v>86.67</v>
       </c>
-      <c r="O65" s="31">
+      <c r="O65" s="29">
         <f t="shared" si="3"/>
         <v>350</v>
       </c>
-      <c r="P65" s="33" t="s">
+      <c r="P65" s="31" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>92</v>
       </c>
@@ -8875,11 +8868,11 @@
       <c r="O66" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="P66" s="29" t="s">
+      <c r="P66" s="1" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>108</v>
       </c>
@@ -8901,32 +8894,32 @@
       <c r="G67" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I67" s="31" t="s">
+      <c r="I67" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="J67" s="32">
+      <c r="J67" s="30">
         <v>45050.083333333336</v>
       </c>
-      <c r="K67" s="31">
-        <v>0</v>
-      </c>
-      <c r="L67" s="31">
+      <c r="K67" s="29">
+        <v>0</v>
+      </c>
+      <c r="L67" s="29">
         <v>96.4</v>
       </c>
-      <c r="M67" s="31">
+      <c r="M67" s="29">
         <v>50.92</v>
       </c>
-      <c r="N67" s="35">
+      <c r="N67" s="33">
         <v>71.05</v>
       </c>
-      <c r="O67" s="47">
+      <c r="O67" s="45">
         <v>351</v>
       </c>
-      <c r="P67" s="33" t="s">
+      <c r="P67" s="31" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>109</v>
       </c>
@@ -8969,11 +8962,11 @@
       <c r="O68" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="P68" s="29" t="s">
+      <c r="P68" s="1" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>108</v>
       </c>
@@ -9016,11 +9009,11 @@
       <c r="O69" s="5">
         <v>352</v>
       </c>
-      <c r="P69" s="29" t="s">
+      <c r="P69" s="1" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>120</v>
       </c>
@@ -9063,30 +9056,30 @@
       <c r="O70" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="P70" s="29" t="s">
+      <c r="P70" s="1" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A71" s="31" t="s">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A71" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="B71" s="32">
+      <c r="B71" s="30">
         <v>45050</v>
       </c>
-      <c r="C71" s="31">
-        <v>0</v>
-      </c>
-      <c r="D71" s="31">
+      <c r="C71" s="29">
+        <v>0</v>
+      </c>
+      <c r="D71" s="29">
         <v>94.1</v>
       </c>
-      <c r="E71" s="31">
+      <c r="E71" s="29">
         <v>77.489999999999995</v>
       </c>
-      <c r="F71" s="31">
+      <c r="F71" s="29">
         <v>86.2</v>
       </c>
-      <c r="G71" s="31" t="s">
+      <c r="G71" s="29" t="s">
         <v>122</v>
       </c>
       <c r="I71" s="2" t="s">
@@ -9110,11 +9103,11 @@
       <c r="O71" s="5">
         <v>353</v>
       </c>
-      <c r="P71" s="29" t="s">
+      <c r="P71" s="1" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>124</v>
       </c>
@@ -9157,105 +9150,105 @@
       <c r="O72" s="5">
         <v>354</v>
       </c>
-      <c r="P72" s="29" t="s">
+      <c r="P72" s="1" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A73" s="31" t="s">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A73" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="B73" s="32">
+      <c r="B73" s="30">
         <v>45050</v>
       </c>
-      <c r="C73" s="31">
-        <v>0</v>
-      </c>
-      <c r="D73" s="31">
+      <c r="C73" s="29">
+        <v>0</v>
+      </c>
+      <c r="D73" s="29">
         <v>96.2</v>
       </c>
-      <c r="E73" s="31">
+      <c r="E73" s="29">
         <v>33.08</v>
       </c>
-      <c r="F73" s="31">
+      <c r="F73" s="29">
         <v>50.79</v>
       </c>
-      <c r="G73" s="31" t="s">
+      <c r="G73" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="I73" s="31" t="s">
+      <c r="I73" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="J73" s="32">
+      <c r="J73" s="30">
         <v>45050.958333333336</v>
       </c>
-      <c r="K73" s="31">
-        <v>0</v>
-      </c>
-      <c r="L73" s="31">
+      <c r="K73" s="29">
+        <v>0</v>
+      </c>
+      <c r="L73" s="29">
         <v>96.2</v>
       </c>
-      <c r="M73" s="31">
+      <c r="M73" s="29">
         <v>33.08</v>
       </c>
-      <c r="N73" s="35">
+      <c r="N73" s="33">
         <v>50.79</v>
       </c>
-      <c r="O73" s="47">
+      <c r="O73" s="45">
         <v>356</v>
       </c>
-      <c r="P73" s="33" t="s">
+      <c r="P73" s="31" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A74" s="31" t="s">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A74" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="B74" s="32">
+      <c r="B74" s="30">
         <v>45050</v>
       </c>
-      <c r="C74" s="31">
-        <v>0</v>
-      </c>
-      <c r="D74" s="31">
+      <c r="C74" s="29">
+        <v>0</v>
+      </c>
+      <c r="D74" s="29">
         <v>96.4</v>
       </c>
-      <c r="E74" s="31">
+      <c r="E74" s="29">
         <v>50.92</v>
       </c>
-      <c r="F74" s="31">
+      <c r="F74" s="29">
         <v>71.05</v>
       </c>
-      <c r="G74" s="31" t="s">
+      <c r="G74" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="I74" s="31" t="s">
+      <c r="I74" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="J74" s="32">
+      <c r="J74" s="30">
         <v>45051.083333333336</v>
       </c>
-      <c r="K74" s="31">
-        <v>0</v>
-      </c>
-      <c r="L74" s="31">
+      <c r="K74" s="29">
+        <v>0</v>
+      </c>
+      <c r="L74" s="29">
         <v>94.1</v>
       </c>
-      <c r="M74" s="31">
+      <c r="M74" s="29">
         <v>77.489999999999995</v>
       </c>
-      <c r="N74" s="35">
+      <c r="N74" s="33">
         <v>86.2</v>
       </c>
-      <c r="O74" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="P74" s="33" t="s">
+      <c r="O74" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="P74" s="31" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>114</v>
       </c>
@@ -9278,145 +9271,145 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A76" s="31" t="s">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A76" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="B76" s="32">
+      <c r="B76" s="30">
         <v>45035</v>
       </c>
-      <c r="C76" s="31">
-        <v>0</v>
-      </c>
-      <c r="D76" s="31">
+      <c r="C76" s="29">
+        <v>0</v>
+      </c>
+      <c r="D76" s="29">
         <v>95.8</v>
       </c>
-      <c r="E76" s="31">
+      <c r="E76" s="29">
         <v>56.35</v>
       </c>
-      <c r="F76" s="31">
+      <c r="F76" s="29">
         <v>57.44</v>
       </c>
-      <c r="G76" s="31" t="s">
+      <c r="G76" s="29" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A77" s="31" t="s">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A77" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="B77" s="32">
+      <c r="B77" s="30">
         <v>45035</v>
       </c>
-      <c r="C77" s="31">
-        <v>0</v>
-      </c>
-      <c r="D77" s="31">
+      <c r="C77" s="29">
+        <v>0</v>
+      </c>
+      <c r="D77" s="29">
         <v>95.7</v>
       </c>
-      <c r="E77" s="31">
+      <c r="E77" s="29">
         <v>57.6</v>
       </c>
-      <c r="F77" s="31">
+      <c r="F77" s="29">
         <v>57.36</v>
       </c>
-      <c r="G77" s="31" t="s">
+      <c r="G77" s="29" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A78" s="31" t="s">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A78" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="B78" s="32">
+      <c r="B78" s="30">
         <v>45035</v>
       </c>
-      <c r="C78" s="31">
-        <v>0</v>
-      </c>
-      <c r="D78" s="31">
+      <c r="C78" s="29">
+        <v>0</v>
+      </c>
+      <c r="D78" s="29">
         <v>95.7</v>
       </c>
-      <c r="E78" s="31">
+      <c r="E78" s="29">
         <v>59.7</v>
       </c>
-      <c r="F78" s="31">
+      <c r="F78" s="29">
         <v>59.08</v>
       </c>
-      <c r="G78" s="31" t="s">
+      <c r="G78" s="29" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A79" s="31" t="s">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A79" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="B79" s="36">
+      <c r="B79" s="34">
         <v>45034</v>
       </c>
-      <c r="C79" s="31">
-        <v>0</v>
-      </c>
-      <c r="D79" s="31">
+      <c r="C79" s="29">
+        <v>0</v>
+      </c>
+      <c r="D79" s="29">
         <v>97.4</v>
       </c>
-      <c r="E79" s="31">
+      <c r="E79" s="29">
         <v>43.36</v>
       </c>
-      <c r="F79" s="31">
+      <c r="F79" s="29">
         <v>82.77</v>
       </c>
-      <c r="G79" s="31" t="s">
+      <c r="G79" s="29" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A80" s="31" t="s">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A80" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="B80" s="36">
+      <c r="B80" s="34">
         <v>45034</v>
       </c>
-      <c r="C80" s="31">
-        <v>0</v>
-      </c>
-      <c r="D80" s="31">
+      <c r="C80" s="29">
+        <v>0</v>
+      </c>
+      <c r="D80" s="29">
         <v>96.9</v>
       </c>
-      <c r="E80" s="31">
+      <c r="E80" s="29">
         <v>46.16</v>
       </c>
-      <c r="F80" s="31">
+      <c r="F80" s="29">
         <v>78.34</v>
       </c>
-      <c r="G80" s="31" t="s">
+      <c r="G80" s="29" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="31" t="s">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="B81" s="36">
+      <c r="B81" s="34">
         <v>45034</v>
       </c>
-      <c r="C81" s="31">
-        <v>0</v>
-      </c>
-      <c r="D81" s="31">
+      <c r="C81" s="29">
+        <v>0</v>
+      </c>
+      <c r="D81" s="29">
         <v>96.7</v>
       </c>
-      <c r="E81" s="31">
+      <c r="E81" s="29">
         <v>46.74</v>
       </c>
-      <c r="F81" s="31">
+      <c r="F81" s="29">
         <v>75.37</v>
       </c>
-      <c r="G81" s="31" t="s">
+      <c r="G81" s="29" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>135</v>
       </c>
@@ -9439,7 +9432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>109</v>
       </c>
@@ -9462,7 +9455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>141</v>
       </c>
@@ -9485,99 +9478,99 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="31" t="s">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="B85" s="36">
+      <c r="B85" s="34">
         <v>45034</v>
       </c>
-      <c r="C85" s="31">
-        <v>0</v>
-      </c>
-      <c r="D85" s="31">
+      <c r="C85" s="29">
+        <v>0</v>
+      </c>
+      <c r="D85" s="29">
         <v>92.3</v>
       </c>
-      <c r="E85" s="31">
+      <c r="E85" s="29">
         <v>75.239999999999995</v>
       </c>
-      <c r="F85" s="31">
+      <c r="F85" s="29">
         <v>45.95</v>
       </c>
-      <c r="G85" s="31" t="s">
+      <c r="G85" s="29" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="31" t="s">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="29" t="s">
         <v>232</v>
       </c>
-      <c r="B86" s="36">
+      <c r="B86" s="34">
         <v>45034</v>
       </c>
-      <c r="C86" s="31">
-        <v>0</v>
-      </c>
-      <c r="D86" s="31">
+      <c r="C86" s="29">
+        <v>0</v>
+      </c>
+      <c r="D86" s="29">
         <v>92.2</v>
       </c>
-      <c r="E86" s="31">
+      <c r="E86" s="29">
         <v>76.430000000000007</v>
       </c>
-      <c r="F86" s="31">
+      <c r="F86" s="29">
         <v>45.44</v>
       </c>
-      <c r="G86" s="31" t="s">
+      <c r="G86" s="29" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="31" t="s">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="B87" s="38">
+      <c r="B87" s="36">
         <v>45034</v>
       </c>
-      <c r="C87" s="31">
-        <v>0</v>
-      </c>
-      <c r="D87" s="31">
+      <c r="C87" s="29">
+        <v>0</v>
+      </c>
+      <c r="D87" s="29">
         <v>92</v>
       </c>
-      <c r="E87" s="31">
+      <c r="E87" s="29">
         <v>82.89</v>
       </c>
-      <c r="F87" s="31">
+      <c r="F87" s="29">
         <v>48.4</v>
       </c>
-      <c r="G87" s="31" t="s">
+      <c r="G87" s="29" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="31" t="s">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="B88" s="36">
+      <c r="B88" s="34">
         <v>45044</v>
       </c>
-      <c r="C88" s="31">
-        <v>0</v>
-      </c>
-      <c r="D88" s="31">
+      <c r="C88" s="29">
+        <v>0</v>
+      </c>
+      <c r="D88" s="29">
         <v>92.2</v>
       </c>
-      <c r="E88" s="31">
+      <c r="E88" s="29">
         <v>80.28</v>
       </c>
-      <c r="F88" s="31">
+      <c r="F88" s="29">
         <v>48.59</v>
       </c>
-      <c r="G88" s="31" t="s">
+      <c r="G88" s="29" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>129</v>
       </c>
@@ -9600,7 +9593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>138</v>
       </c>
@@ -9623,7 +9616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>134</v>
       </c>
@@ -9646,76 +9639,76 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="31" t="s">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="B92" s="36">
+      <c r="B92" s="34">
         <v>45037</v>
       </c>
-      <c r="C92" s="31">
-        <v>0</v>
-      </c>
-      <c r="D92" s="31">
+      <c r="C92" s="29">
+        <v>0</v>
+      </c>
+      <c r="D92" s="29">
         <v>97.2</v>
       </c>
-      <c r="E92" s="31">
+      <c r="E92" s="29">
         <v>39.35</v>
       </c>
-      <c r="F92" s="31">
+      <c r="F92" s="29">
         <v>72.25</v>
       </c>
-      <c r="G92" s="31" t="s">
+      <c r="G92" s="29" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="31" t="s">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="B93" s="36">
+      <c r="B93" s="34">
         <v>45037</v>
       </c>
-      <c r="C93" s="31">
-        <v>0</v>
-      </c>
-      <c r="D93" s="31">
+      <c r="C93" s="29">
+        <v>0</v>
+      </c>
+      <c r="D93" s="29">
         <v>97.2</v>
       </c>
-      <c r="E93" s="31">
+      <c r="E93" s="29">
         <v>31.45</v>
       </c>
-      <c r="F93" s="31">
+      <c r="F93" s="29">
         <v>59.67</v>
       </c>
-      <c r="G93" s="31" t="s">
+      <c r="G93" s="29" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="31" t="s">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="B94" s="36">
+      <c r="B94" s="34">
         <v>45037</v>
       </c>
-      <c r="C94" s="31">
-        <v>0</v>
-      </c>
-      <c r="D94" s="31">
+      <c r="C94" s="29">
+        <v>0</v>
+      </c>
+      <c r="D94" s="29">
         <v>97.1</v>
       </c>
-      <c r="E94" s="31">
+      <c r="E94" s="29">
         <v>38.119999999999997</v>
       </c>
-      <c r="F94" s="31">
+      <c r="F94" s="29">
         <v>67.28</v>
       </c>
-      <c r="G94" s="31" t="s">
+      <c r="G94" s="29" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>121</v>
       </c>
@@ -9738,99 +9731,99 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="31" t="s">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="B96" s="36">
+      <c r="B96" s="34">
         <v>45035</v>
       </c>
-      <c r="C96" s="31">
-        <v>0</v>
-      </c>
-      <c r="D96" s="31">
+      <c r="C96" s="29">
+        <v>0</v>
+      </c>
+      <c r="D96" s="29">
         <v>95.3</v>
       </c>
-      <c r="E96" s="31">
+      <c r="E96" s="29">
         <v>61.54</v>
       </c>
-      <c r="F96" s="31">
+      <c r="F96" s="29">
         <v>60.65</v>
       </c>
-      <c r="G96" s="31" t="s">
+      <c r="G96" s="29" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="31" t="s">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="B97" s="36">
+      <c r="B97" s="34">
         <v>45035</v>
       </c>
-      <c r="C97" s="31">
-        <v>0</v>
-      </c>
-      <c r="D97" s="31">
+      <c r="C97" s="29">
+        <v>0</v>
+      </c>
+      <c r="D97" s="29">
         <v>95.1</v>
       </c>
-      <c r="E97" s="31">
+      <c r="E97" s="29">
         <v>66.89</v>
       </c>
-      <c r="F97" s="31">
+      <c r="F97" s="29">
         <v>64.42</v>
       </c>
-      <c r="G97" s="31" t="s">
+      <c r="G97" s="29" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="31" t="s">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="B98" s="36">
+      <c r="B98" s="34">
         <v>45035</v>
       </c>
-      <c r="C98" s="31">
-        <v>0</v>
-      </c>
-      <c r="D98" s="31">
+      <c r="C98" s="29">
+        <v>0</v>
+      </c>
+      <c r="D98" s="29">
         <v>95</v>
       </c>
-      <c r="E98" s="31">
+      <c r="E98" s="29">
         <v>84.06</v>
       </c>
-      <c r="F98" s="31">
+      <c r="F98" s="29">
         <v>74.489999999999995</v>
       </c>
-      <c r="G98" s="31" t="s">
+      <c r="G98" s="29" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="31" t="s">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="B99" s="36">
+      <c r="B99" s="34">
         <v>45035</v>
       </c>
-      <c r="C99" s="31">
-        <v>0</v>
-      </c>
-      <c r="D99" s="31">
+      <c r="C99" s="29">
+        <v>0</v>
+      </c>
+      <c r="D99" s="29">
         <v>94.9</v>
       </c>
-      <c r="E99" s="31">
+      <c r="E99" s="29">
         <v>86.52</v>
       </c>
-      <c r="F99" s="31">
+      <c r="F99" s="29">
         <v>75.91</v>
       </c>
-      <c r="G99" s="31" t="s">
+      <c r="G99" s="29" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>120</v>
       </c>
@@ -9853,7 +9846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101"/>
       <c r="B101"/>
       <c r="C101"/>
@@ -9862,7 +9855,7 @@
       <c r="F101"/>
       <c r="G101"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102"/>
       <c r="B102"/>
       <c r="C102"/>
@@ -9871,7 +9864,7 @@
       <c r="F102"/>
       <c r="G102"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103"/>
       <c r="B103"/>
       <c r="C103"/>
@@ -9880,7 +9873,7 @@
       <c r="F103"/>
       <c r="G103"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104"/>
       <c r="B104"/>
       <c r="C104"/>
@@ -9889,7 +9882,7 @@
       <c r="F104"/>
       <c r="G104"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105"/>
       <c r="B105"/>
       <c r="C105"/>
@@ -9898,7 +9891,7 @@
       <c r="F105"/>
       <c r="G105"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106"/>
       <c r="B106"/>
       <c r="C106"/>
@@ -9907,7 +9900,7 @@
       <c r="F106"/>
       <c r="G106"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107"/>
       <c r="B107"/>
       <c r="C107"/>
@@ -9916,7 +9909,7 @@
       <c r="F107"/>
       <c r="G107"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108"/>
       <c r="B108"/>
       <c r="C108"/>
@@ -9925,7 +9918,7 @@
       <c r="F108"/>
       <c r="G108"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109"/>
       <c r="B109"/>
       <c r="C109"/>
@@ -9934,7 +9927,7 @@
       <c r="F109"/>
       <c r="G109"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110"/>
       <c r="B110"/>
       <c r="C110"/>
@@ -9943,7 +9936,7 @@
       <c r="F110"/>
       <c r="G110"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111"/>
       <c r="B111"/>
       <c r="C111"/>
@@ -9952,7 +9945,7 @@
       <c r="F111"/>
       <c r="G111"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112"/>
       <c r="B112"/>
       <c r="C112"/>
@@ -9961,125 +9954,125 @@
       <c r="F112"/>
       <c r="G112"/>
     </row>
-    <row r="113" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P113" s="29"/>
-    </row>
-    <row r="114" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P114" s="29"/>
-    </row>
-    <row r="115" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P115" s="29"/>
-    </row>
-    <row r="116" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P116" s="29"/>
-    </row>
-    <row r="117" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P117" s="29"/>
-    </row>
-    <row r="118" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P118" s="29"/>
-    </row>
-    <row r="119" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P119" s="29"/>
-    </row>
-    <row r="120" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P120" s="29"/>
-    </row>
-    <row r="121" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P121" s="29"/>
-    </row>
-    <row r="122" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P122" s="29"/>
-    </row>
-    <row r="123" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P123" s="29"/>
-    </row>
-    <row r="124" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P124" s="29"/>
-    </row>
-    <row r="125" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P125" s="29"/>
-    </row>
-    <row r="126" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P126" s="29"/>
-    </row>
-    <row r="127" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P127" s="29"/>
-    </row>
-    <row r="128" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P128" s="29"/>
-    </row>
-    <row r="129" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P129" s="29"/>
-    </row>
-    <row r="130" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P130" s="29"/>
-    </row>
-    <row r="131" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P131" s="29"/>
-    </row>
-    <row r="132" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P132" s="29"/>
-    </row>
-    <row r="133" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P133" s="29"/>
-    </row>
-    <row r="134" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P134" s="29"/>
-    </row>
-    <row r="135" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P135" s="29"/>
-    </row>
-    <row r="136" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P136" s="29"/>
-    </row>
-    <row r="137" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P137" s="29"/>
-    </row>
-    <row r="138" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P138" s="29"/>
-    </row>
-    <row r="139" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P139" s="29"/>
-    </row>
-    <row r="140" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P140" s="29"/>
-    </row>
-    <row r="141" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P141" s="29"/>
-    </row>
-    <row r="142" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P142" s="29"/>
-    </row>
-    <row r="143" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P143" s="29"/>
-    </row>
-    <row r="144" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P144" s="29"/>
-    </row>
-    <row r="145" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P145" s="29"/>
-    </row>
-    <row r="146" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P146" s="29"/>
-    </row>
-    <row r="147" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P147" s="29"/>
-    </row>
-    <row r="148" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P148" s="29"/>
-    </row>
-    <row r="149" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P149" s="29"/>
-    </row>
-    <row r="150" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P150" s="29"/>
-    </row>
-    <row r="151" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P151" s="29"/>
-    </row>
-    <row r="152" spans="16:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P152" s="29"/>
+    <row r="113" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P113" s="1"/>
+    </row>
+    <row r="114" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P114" s="1"/>
+    </row>
+    <row r="115" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P115" s="1"/>
+    </row>
+    <row r="116" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P116" s="1"/>
+    </row>
+    <row r="117" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P117" s="1"/>
+    </row>
+    <row r="118" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P118" s="1"/>
+    </row>
+    <row r="119" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P119" s="1"/>
+    </row>
+    <row r="120" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P120" s="1"/>
+    </row>
+    <row r="121" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P121" s="1"/>
+    </row>
+    <row r="122" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P122" s="1"/>
+    </row>
+    <row r="123" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P123" s="1"/>
+    </row>
+    <row r="124" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P124" s="1"/>
+    </row>
+    <row r="125" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P125" s="1"/>
+    </row>
+    <row r="126" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P126" s="1"/>
+    </row>
+    <row r="127" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P127" s="1"/>
+    </row>
+    <row r="128" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P128" s="1"/>
+    </row>
+    <row r="129" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P129" s="1"/>
+    </row>
+    <row r="130" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P130" s="1"/>
+    </row>
+    <row r="131" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P131" s="1"/>
+    </row>
+    <row r="132" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P132" s="1"/>
+    </row>
+    <row r="133" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P133" s="1"/>
+    </row>
+    <row r="134" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P134" s="1"/>
+    </row>
+    <row r="135" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P135" s="1"/>
+    </row>
+    <row r="136" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P136" s="1"/>
+    </row>
+    <row r="137" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P137" s="1"/>
+    </row>
+    <row r="138" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P138" s="1"/>
+    </row>
+    <row r="139" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P139" s="1"/>
+    </row>
+    <row r="140" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P140" s="1"/>
+    </row>
+    <row r="141" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P141" s="1"/>
+    </row>
+    <row r="142" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P142" s="1"/>
+    </row>
+    <row r="143" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P143" s="1"/>
+    </row>
+    <row r="144" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P144" s="1"/>
+    </row>
+    <row r="145" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P145" s="1"/>
+    </row>
+    <row r="146" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P146" s="1"/>
+    </row>
+    <row r="147" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P147" s="1"/>
+    </row>
+    <row r="148" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P148" s="1"/>
+    </row>
+    <row r="149" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P149" s="1"/>
+    </row>
+    <row r="150" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P150" s="1"/>
+    </row>
+    <row r="151" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P151" s="1"/>
+    </row>
+    <row r="152" spans="16:16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P152" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:N100" xr:uid="{DC4F41F3-2406-4DBC-AD18-012969672032}">
@@ -10100,35 +10093,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47770336-139B-4E1D-B90D-A41F00945441}">
   <dimension ref="A2:W156"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="1"/>
-    <col min="4" max="4" width="17.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="17.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.6640625" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" style="1"/>
-    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" customWidth="1"/>
-    <col min="15" max="15" width="19.5703125" customWidth="1"/>
+    <col min="11" max="11" width="19.88671875" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" style="1"/>
+    <col min="13" max="13" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.5546875" customWidth="1"/>
+    <col min="15" max="15" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="Q2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="54" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="55"/>
+      <c r="B3" s="52"/>
       <c r="C3" s="16" t="s">
         <v>1</v>
       </c>
@@ -10144,7 +10137,7 @@
       <c r="G3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="28" t="s">
         <v>340</v>
       </c>
       <c r="J3" s="26" t="s">
@@ -10169,7 +10162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -10191,32 +10184,32 @@
       <c r="G4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="31" t="s">
+      <c r="J4" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="34">
         <v>45033.6875</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="29">
         <v>190</v>
       </c>
-      <c r="M4" s="31">
-        <v>0</v>
-      </c>
-      <c r="N4" s="34">
+      <c r="M4" s="29">
+        <v>0</v>
+      </c>
+      <c r="N4" s="32">
         <v>93.4</v>
       </c>
-      <c r="O4" s="34">
+      <c r="O4" s="32">
         <v>103.30500000000001</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="32">
         <v>81.800000000000011</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -10238,79 +10231,79 @@
       <c r="G5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I5" s="33" t="s">
+      <c r="I5" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="J5" s="45" t="s">
+      <c r="J5" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="44">
         <v>45033.854166666664</v>
       </c>
-      <c r="L5" s="31">
+      <c r="L5" s="29">
         <v>191</v>
       </c>
-      <c r="M5" s="31">
-        <v>0</v>
-      </c>
-      <c r="N5" s="34">
+      <c r="M5" s="29">
+        <v>0</v>
+      </c>
+      <c r="N5" s="32">
         <v>94.4</v>
       </c>
-      <c r="O5" s="34">
+      <c r="O5" s="32">
         <v>65.48</v>
       </c>
-      <c r="P5" s="34">
+      <c r="P5" s="32">
         <v>51.72</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="30">
         <v>45049</v>
       </c>
-      <c r="C6" s="31">
-        <v>0</v>
-      </c>
-      <c r="D6" s="31">
+      <c r="C6" s="29">
+        <v>0</v>
+      </c>
+      <c r="D6" s="29">
         <v>96.4</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="29">
         <v>39.619999999999997</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="29">
         <v>54.92</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="33" t="s">
+      <c r="I6" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="J6" s="50" t="s">
+      <c r="J6" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="K6" s="32">
+      <c r="K6" s="30">
         <v>45034.020833333336</v>
       </c>
-      <c r="L6" s="31">
+      <c r="L6" s="29">
         <v>192</v>
       </c>
-      <c r="M6" s="31">
-        <v>0</v>
-      </c>
-      <c r="N6" s="34">
+      <c r="M6" s="29">
+        <v>0</v>
+      </c>
+      <c r="N6" s="32">
         <v>97.05</v>
       </c>
-      <c r="O6" s="34">
+      <c r="O6" s="32">
         <v>73.675000000000011</v>
       </c>
-      <c r="P6" s="34">
+      <c r="P6" s="32">
         <v>91.46</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>12</v>
       </c>
@@ -10332,35 +10325,35 @@
       <c r="G7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="56" t="s">
+      <c r="H7" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="33" t="s">
+      <c r="I7" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="J7" s="31" t="s">
+      <c r="J7" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="K7" s="36">
+      <c r="K7" s="34">
         <v>45034.1875</v>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="29">
         <v>193</v>
       </c>
-      <c r="M7" s="31">
-        <v>0</v>
-      </c>
-      <c r="N7" s="34">
+      <c r="M7" s="29">
+        <v>0</v>
+      </c>
+      <c r="N7" s="32">
         <v>96.9</v>
       </c>
-      <c r="O7" s="34">
+      <c r="O7" s="32">
         <v>48.895000000000003</v>
       </c>
-      <c r="P7" s="34">
+      <c r="P7" s="32">
         <v>58.709999999999994</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
         <v>14</v>
       </c>
@@ -10382,8 +10375,8 @@
       <c r="G8" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="56"/>
-      <c r="I8" s="29" t="s">
+      <c r="H8" s="53"/>
+      <c r="I8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J8" s="8" t="s">
@@ -10392,7 +10385,7 @@
       <c r="K8" s="3">
         <v>45034.354166666664</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="2">
         <v>211</v>
       </c>
       <c r="M8" s="2">
@@ -10411,7 +10404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>16</v>
       </c>
@@ -10433,8 +10426,8 @@
       <c r="G9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="56"/>
-      <c r="I9" s="29" t="s">
+      <c r="H9" s="53"/>
+      <c r="I9" s="1" t="s">
         <v>102</v>
       </c>
       <c r="J9" s="2" t="s">
@@ -10462,7 +10455,7 @@
         <v>5.7697015333333299</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>23</v>
       </c>
@@ -10484,33 +10477,33 @@
       <c r="G10" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="56"/>
-      <c r="I10" s="33" t="s">
+      <c r="H10" s="53"/>
+      <c r="I10" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="K10" s="36">
+      <c r="K10" s="34">
         <v>45034.6875</v>
       </c>
-      <c r="L10" s="31">
+      <c r="L10" s="29">
         <v>213</v>
       </c>
-      <c r="M10" s="31">
-        <v>0</v>
-      </c>
-      <c r="N10" s="34">
+      <c r="M10" s="29">
+        <v>0</v>
+      </c>
+      <c r="N10" s="32">
         <v>92.949999999999989</v>
       </c>
-      <c r="O10" s="34">
+      <c r="O10" s="32">
         <v>93.474999999999994</v>
       </c>
-      <c r="P10" s="34">
+      <c r="P10" s="32">
         <v>56.024999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>24</v>
       </c>
@@ -10532,33 +10525,33 @@
       <c r="G11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="56"/>
-      <c r="I11" s="33" t="s">
+      <c r="H11" s="53"/>
+      <c r="I11" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="J11" s="43" t="s">
+      <c r="J11" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="K11" s="44">
+      <c r="K11" s="42">
         <v>45034.895833333336</v>
       </c>
-      <c r="L11" s="31">
+      <c r="L11" s="29">
         <v>214</v>
       </c>
-      <c r="M11" s="31">
-        <v>0</v>
-      </c>
-      <c r="N11" s="34">
+      <c r="M11" s="29">
+        <v>0</v>
+      </c>
+      <c r="N11" s="32">
         <v>95.55</v>
       </c>
-      <c r="O11" s="34">
+      <c r="O11" s="32">
         <v>53.784999999999997</v>
       </c>
-      <c r="P11" s="34">
+      <c r="P11" s="32">
         <v>66.137500000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>25</v>
       </c>
@@ -10580,33 +10573,33 @@
       <c r="G12" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="56"/>
-      <c r="I12" s="33" t="s">
+      <c r="H12" s="53"/>
+      <c r="I12" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="J12" s="31" t="s">
+      <c r="J12" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="K12" s="36">
+      <c r="K12" s="34">
         <v>45035.104166666664</v>
       </c>
-      <c r="L12" s="31">
+      <c r="L12" s="29">
         <v>215</v>
       </c>
-      <c r="M12" s="31">
-        <v>0</v>
-      </c>
-      <c r="N12" s="34">
+      <c r="M12" s="29">
+        <v>0</v>
+      </c>
+      <c r="N12" s="32">
         <v>96.633333333333326</v>
       </c>
-      <c r="O12" s="34">
+      <c r="O12" s="32">
         <v>47.579999999999991</v>
       </c>
-      <c r="P12" s="34">
+      <c r="P12" s="32">
         <v>57.156666666666666</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>26</v>
       </c>
@@ -10628,33 +10621,33 @@
       <c r="G13" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="56"/>
-      <c r="I13" s="33" t="s">
+      <c r="H13" s="53"/>
+      <c r="I13" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="J13" s="31" t="s">
+      <c r="J13" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="K13" s="36">
+      <c r="K13" s="34">
         <v>45035.3125</v>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="29">
         <v>216</v>
       </c>
-      <c r="M13" s="31">
-        <v>0</v>
-      </c>
-      <c r="N13" s="34">
+      <c r="M13" s="29">
+        <v>0</v>
+      </c>
+      <c r="N13" s="32">
         <v>97.066666666666677</v>
       </c>
-      <c r="O13" s="34">
+      <c r="O13" s="32">
         <v>30.72</v>
       </c>
-      <c r="P13" s="34">
+      <c r="P13" s="32">
         <v>47.137500000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>27</v>
       </c>
@@ -10676,8 +10669,8 @@
       <c r="G14" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="56"/>
-      <c r="I14" s="29" t="s">
+      <c r="H14" s="53"/>
+      <c r="I14" s="1" t="s">
         <v>104</v>
       </c>
       <c r="J14" s="10" t="s">
@@ -10705,7 +10698,7 @@
         <v>10.820681333333299</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>28</v>
       </c>
@@ -10727,8 +10720,8 @@
       <c r="G15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="56"/>
-      <c r="I15" s="29" t="s">
+      <c r="H15" s="53"/>
+      <c r="I15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="J15" s="5" t="s">
@@ -10756,7 +10749,7 @@
         <v>16.381029333333299</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>29</v>
       </c>
@@ -10778,33 +10771,33 @@
       <c r="G16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="56"/>
-      <c r="I16" s="33" t="s">
+      <c r="H16" s="53"/>
+      <c r="I16" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="J16" s="48" t="s">
+      <c r="J16" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="K16" s="49">
+      <c r="K16" s="47">
         <v>45035.9375</v>
       </c>
-      <c r="L16" s="31">
+      <c r="L16" s="29">
         <v>219</v>
       </c>
-      <c r="M16" s="31">
-        <v>0</v>
-      </c>
-      <c r="N16" s="34">
+      <c r="M16" s="29">
+        <v>0</v>
+      </c>
+      <c r="N16" s="32">
         <v>96.800000000000011</v>
       </c>
-      <c r="O16" s="34">
+      <c r="O16" s="32">
         <v>22.36</v>
       </c>
-      <c r="P16" s="34">
+      <c r="P16" s="32">
         <v>38.814999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>30</v>
       </c>
@@ -10826,33 +10819,33 @@
       <c r="G17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="56"/>
-      <c r="I17" s="33" t="s">
+      <c r="H17" s="53"/>
+      <c r="I17" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="J17" s="47" t="s">
+      <c r="J17" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="K17" s="49">
+      <c r="K17" s="47">
         <v>45036.145833333336</v>
       </c>
-      <c r="L17" s="31">
+      <c r="L17" s="29">
         <v>220</v>
       </c>
-      <c r="M17" s="31">
-        <v>0</v>
-      </c>
-      <c r="N17" s="34">
+      <c r="M17" s="29">
+        <v>0</v>
+      </c>
+      <c r="N17" s="32">
         <v>96.8</v>
       </c>
-      <c r="O17" s="34">
+      <c r="O17" s="32">
         <v>30.83</v>
       </c>
-      <c r="P17" s="34">
+      <c r="P17" s="32">
         <v>52.1</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
         <v>40</v>
       </c>
@@ -10874,8 +10867,8 @@
       <c r="G18" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="56"/>
-      <c r="I18" s="29" t="s">
+      <c r="H18" s="53"/>
+      <c r="I18" s="1" t="s">
         <v>95</v>
       </c>
       <c r="J18" s="2" t="s">
@@ -10899,11 +10892,11 @@
       <c r="P18" s="22">
         <v>0</v>
       </c>
-      <c r="Q18" s="58">
+      <c r="Q18">
         <v>11.302605</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>41</v>
       </c>
@@ -10925,8 +10918,8 @@
       <c r="G19" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="56"/>
-      <c r="I19" s="29" t="s">
+      <c r="H19" s="53"/>
+      <c r="I19" s="1" t="s">
         <v>77</v>
       </c>
       <c r="J19" s="2" t="s">
@@ -10950,11 +10943,11 @@
       <c r="P19" s="22">
         <v>0</v>
       </c>
-      <c r="Q19" s="58">
+      <c r="Q19">
         <v>12.379865893333299</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
         <v>42</v>
       </c>
@@ -10976,29 +10969,29 @@
       <c r="G20" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="56"/>
-      <c r="I20" s="33" t="s">
+      <c r="H20" s="53"/>
+      <c r="I20" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="J20" s="48" t="s">
+      <c r="J20" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="K20" s="49">
+      <c r="K20" s="47">
         <v>45036.979166666664</v>
       </c>
-      <c r="L20" s="31">
+      <c r="L20" s="29">
         <v>237</v>
       </c>
-      <c r="M20" s="31">
-        <v>0</v>
-      </c>
-      <c r="N20" s="34">
+      <c r="M20" s="29">
+        <v>0</v>
+      </c>
+      <c r="N20" s="32">
         <v>97</v>
       </c>
-      <c r="O20" s="34">
+      <c r="O20" s="32">
         <v>24.91</v>
       </c>
-      <c r="P20" s="34">
+      <c r="P20" s="32">
         <v>58.21</v>
       </c>
       <c r="S20" t="s">
@@ -11012,7 +11005,7 @@
         <v>5.7697015333333299</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>43</v>
       </c>
@@ -11034,8 +11027,8 @@
       <c r="G21" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="H21" s="56"/>
-      <c r="I21" s="29" t="s">
+      <c r="H21" s="53"/>
+      <c r="I21" s="1" t="s">
         <v>101</v>
       </c>
       <c r="J21" s="7" t="s">
@@ -11073,7 +11066,7 @@
         <v>10.820681333333299</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
         <v>44</v>
       </c>
@@ -11095,8 +11088,8 @@
       <c r="G22" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="H22" s="56"/>
-      <c r="I22" s="29" t="s">
+      <c r="H22" s="53"/>
+      <c r="I22" s="1" t="s">
         <v>133</v>
       </c>
       <c r="J22" s="7" t="s">
@@ -11134,7 +11127,7 @@
         <v>16.381029333333299</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>45</v>
       </c>
@@ -11156,29 +11149,29 @@
       <c r="G23" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="56"/>
-      <c r="I23" s="33" t="s">
+      <c r="H23" s="53"/>
+      <c r="I23" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="J23" s="43" t="s">
+      <c r="J23" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="K23" s="44">
+      <c r="K23" s="42">
         <v>45037.8125</v>
       </c>
-      <c r="L23" s="31">
+      <c r="L23" s="29">
         <v>240</v>
       </c>
-      <c r="M23" s="31">
-        <v>0</v>
-      </c>
-      <c r="N23" s="34">
+      <c r="M23" s="29">
+        <v>0</v>
+      </c>
+      <c r="N23" s="32">
         <v>95.85</v>
       </c>
-      <c r="O23" s="34">
+      <c r="O23" s="32">
         <v>67.125</v>
       </c>
-      <c r="P23" s="34">
+      <c r="P23" s="32">
         <v>75.8</v>
       </c>
       <c r="S23" t="s">
@@ -11188,11 +11181,11 @@
         <f>MEDIAN(W20:W68)</f>
         <v>8.70769666666666</v>
       </c>
-      <c r="W23" s="58">
+      <c r="W23">
         <v>11.302605</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
         <v>47</v>
       </c>
@@ -11214,8 +11207,8 @@
       <c r="G24" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="H24" s="56"/>
-      <c r="I24" s="29" t="s">
+      <c r="H24" s="53"/>
+      <c r="I24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J24" s="2" t="s">
@@ -11242,11 +11235,11 @@
       <c r="Q24">
         <v>10.3409056666666</v>
       </c>
-      <c r="W24" s="58">
+      <c r="W24">
         <v>12.379865893333299</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>48</v>
       </c>
@@ -11268,61 +11261,61 @@
       <c r="G25" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="H25" s="56"/>
-      <c r="I25" s="33" t="s">
+      <c r="H25" s="53"/>
+      <c r="I25" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="J25" s="41" t="s">
+      <c r="J25" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="K25" s="42">
+      <c r="K25" s="40">
         <v>45038.229166666664</v>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="29">
         <v>242</v>
       </c>
-      <c r="M25" s="31">
-        <v>0</v>
-      </c>
-      <c r="N25" s="34">
+      <c r="M25" s="29">
+        <v>0</v>
+      </c>
+      <c r="N25" s="32">
         <v>96.974999999999994</v>
       </c>
-      <c r="O25" s="34">
+      <c r="O25" s="32">
         <v>51.682499999999997</v>
       </c>
-      <c r="P25" s="34">
+      <c r="P25" s="32">
         <v>80.920000000000016</v>
       </c>
       <c r="W25">
         <v>7.9286783333333304</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+    <row r="26" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="30">
         <v>45050</v>
       </c>
-      <c r="C26" s="31">
-        <v>0</v>
-      </c>
-      <c r="D26" s="31">
+      <c r="C26" s="29">
+        <v>0</v>
+      </c>
+      <c r="D26" s="29">
         <v>96.2</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="29">
         <v>25.16</v>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="29">
         <v>30.57</v>
       </c>
-      <c r="G26" s="31" t="s">
+      <c r="G26" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="H26" s="53" t="s">
+      <c r="H26" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="I26" s="29" t="s">
+      <c r="I26" s="1" t="s">
         <v>155</v>
       </c>
       <c r="J26" s="10" t="s">
@@ -11353,7 +11346,7 @@
         <v>9.2900002666666595</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
         <v>52</v>
       </c>
@@ -11375,36 +11368,36 @@
       <c r="G27" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="53"/>
-      <c r="I27" s="33" t="s">
+      <c r="H27" s="50"/>
+      <c r="I27" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="J27" s="45" t="s">
+      <c r="J27" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="K27" s="46">
+      <c r="K27" s="44">
         <v>45038.645833333336</v>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="29">
         <v>244</v>
       </c>
-      <c r="M27" s="31">
-        <v>0</v>
-      </c>
-      <c r="N27" s="34">
+      <c r="M27" s="29">
+        <v>0</v>
+      </c>
+      <c r="N27" s="32">
         <v>96.333333333333329</v>
       </c>
-      <c r="O27" s="34">
+      <c r="O27" s="32">
         <v>57.56</v>
       </c>
-      <c r="P27" s="34">
+      <c r="P27" s="32">
         <v>65.026666666666657</v>
       </c>
       <c r="W27">
         <v>10.3409056666666</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
         <v>55</v>
       </c>
@@ -11426,36 +11419,36 @@
       <c r="G28" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="H28" s="53"/>
-      <c r="I28" s="33" t="s">
+      <c r="H28" s="50"/>
+      <c r="I28" s="31" t="s">
         <v>341</v>
       </c>
-      <c r="J28" s="41" t="s">
+      <c r="J28" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="K28" s="42">
+      <c r="K28" s="40">
         <v>45038.854166666664</v>
       </c>
-      <c r="L28" s="31">
+      <c r="L28" s="29">
         <v>245</v>
       </c>
-      <c r="M28" s="31">
-        <v>0</v>
-      </c>
-      <c r="N28" s="34">
+      <c r="M28" s="29">
+        <v>0</v>
+      </c>
+      <c r="N28" s="32">
         <v>95.375000000000014</v>
       </c>
-      <c r="O28" s="34">
+      <c r="O28" s="32">
         <v>63.535000000000011</v>
       </c>
-      <c r="P28" s="34">
+      <c r="P28" s="32">
         <v>59.204999999999998</v>
       </c>
       <c r="W28">
         <v>6.6124433333333297</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" s="18" t="s">
         <v>59</v>
       </c>
@@ -11477,8 +11470,8 @@
       <c r="G29" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="H29" s="53"/>
-      <c r="I29" s="29" t="s">
+      <c r="H29" s="50"/>
+      <c r="I29" s="1" t="s">
         <v>342</v>
       </c>
       <c r="J29" s="14" t="s">
@@ -11509,7 +11502,7 @@
         <v>6.3972824666666597</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" s="18" t="s">
         <v>61</v>
       </c>
@@ -11531,8 +11524,8 @@
       <c r="G30" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="H30" s="53"/>
-      <c r="I30" s="29" t="s">
+      <c r="H30" s="50"/>
+      <c r="I30" s="1" t="s">
         <v>343</v>
       </c>
       <c r="J30" s="2" t="s">
@@ -11563,30 +11556,30 @@
         <v>6.9635272666666603</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A31" s="31" t="s">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A31" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="30">
         <v>45050</v>
       </c>
-      <c r="C31" s="31">
-        <v>0</v>
-      </c>
-      <c r="D31" s="31">
+      <c r="C31" s="29">
+        <v>0</v>
+      </c>
+      <c r="D31" s="29">
         <v>97.1</v>
       </c>
-      <c r="E31" s="31">
+      <c r="E31" s="29">
         <v>21.91</v>
       </c>
-      <c r="F31" s="31">
+      <c r="F31" s="29">
         <v>39.799999999999997</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="G31" s="29" t="s">
         <v>65</v>
       </c>
       <c r="H31" s="20"/>
-      <c r="I31" s="29" t="s">
+      <c r="I31" s="1" t="s">
         <v>344</v>
       </c>
       <c r="J31" s="2" t="s">
@@ -11617,30 +11610,30 @@
         <v>11.1684686666666</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A32" s="31" t="s">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A32" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="38">
+      <c r="B32" s="36">
         <v>45050</v>
       </c>
-      <c r="C32" s="31">
-        <v>0</v>
-      </c>
-      <c r="D32" s="31">
+      <c r="C32" s="29">
+        <v>0</v>
+      </c>
+      <c r="D32" s="29">
         <v>97.1</v>
       </c>
-      <c r="E32" s="31">
+      <c r="E32" s="29">
         <v>23.65</v>
       </c>
-      <c r="F32" s="31">
+      <c r="F32" s="29">
         <v>40.67</v>
       </c>
-      <c r="G32" s="31" t="s">
+      <c r="G32" s="29" t="s">
         <v>66</v>
       </c>
       <c r="H32" s="20"/>
-      <c r="I32" s="29" t="s">
+      <c r="I32" s="1" t="s">
         <v>345</v>
       </c>
       <c r="J32" s="7" t="s">
@@ -11671,82 +11664,82 @@
         <v>8.2048614000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A33" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="32">
+      <c r="B33" s="30">
         <v>45050</v>
       </c>
-      <c r="C33" s="31">
-        <v>0</v>
-      </c>
-      <c r="D33" s="31">
+      <c r="C33" s="29">
+        <v>0</v>
+      </c>
+      <c r="D33" s="29">
         <v>97</v>
       </c>
-      <c r="E33" s="31">
-        <v>0</v>
-      </c>
-      <c r="F33" s="31">
-        <v>0</v>
-      </c>
-      <c r="G33" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I33" s="33" t="s">
+      <c r="E33" s="29">
+        <v>0</v>
+      </c>
+      <c r="F33" s="29">
+        <v>0</v>
+      </c>
+      <c r="G33" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="I33" s="31" t="s">
         <v>346</v>
       </c>
-      <c r="J33" s="31" t="s">
+      <c r="J33" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="K33" s="49">
+      <c r="K33" s="47">
         <v>45040.083333333336</v>
       </c>
-      <c r="L33" s="31">
+      <c r="L33" s="29">
         <v>250</v>
       </c>
-      <c r="M33" s="31">
-        <v>0</v>
-      </c>
-      <c r="N33" s="34">
+      <c r="M33" s="29">
+        <v>0</v>
+      </c>
+      <c r="N33" s="32">
         <v>97.3</v>
       </c>
-      <c r="O33" s="34">
+      <c r="O33" s="32">
         <v>66.586666666666673</v>
       </c>
-      <c r="P33" s="34">
+      <c r="P33" s="32">
         <v>69.806666666666658</v>
       </c>
       <c r="W33">
         <v>6.5715940000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="31" t="s">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A34" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="30">
         <v>45049</v>
       </c>
-      <c r="C34" s="31">
-        <v>0</v>
-      </c>
-      <c r="D34" s="31">
+      <c r="C34" s="29">
+        <v>0</v>
+      </c>
+      <c r="D34" s="29">
         <v>91.6</v>
       </c>
-      <c r="E34" s="31">
+      <c r="E34" s="29">
         <v>76.510000000000005</v>
       </c>
-      <c r="F34" s="31">
+      <c r="F34" s="29">
         <v>45.79</v>
       </c>
-      <c r="G34" s="31" t="s">
+      <c r="G34" s="29" t="s">
         <v>70</v>
       </c>
       <c r="H34" t="s">
         <v>72</v>
       </c>
-      <c r="I34" s="29" t="s">
+      <c r="I34" s="1" t="s">
         <v>347</v>
       </c>
       <c r="J34" s="7" t="s">
@@ -11773,186 +11766,186 @@
       <c r="Q34">
         <v>6.5715940000000002</v>
       </c>
-      <c r="W34" s="59">
+      <c r="W34" s="49">
         <v>7.3385368</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A35" s="31" t="s">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A35" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="32">
+      <c r="B35" s="30">
         <v>45049</v>
       </c>
-      <c r="C35" s="31">
-        <v>0</v>
-      </c>
-      <c r="D35" s="31">
+      <c r="C35" s="29">
+        <v>0</v>
+      </c>
+      <c r="D35" s="29">
         <v>90.9</v>
       </c>
-      <c r="E35" s="31">
+      <c r="E35" s="29">
         <v>94.09</v>
       </c>
-      <c r="F35" s="31">
+      <c r="F35" s="29">
         <v>53.77</v>
       </c>
-      <c r="G35" s="31" t="s">
+      <c r="G35" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="I35" s="33" t="s">
+      <c r="I35" s="31" t="s">
         <v>348</v>
       </c>
-      <c r="J35" s="45" t="s">
+      <c r="J35" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="K35" s="46">
+      <c r="K35" s="44">
         <v>45040.5</v>
       </c>
-      <c r="L35" s="31">
+      <c r="L35" s="29">
         <v>252</v>
       </c>
-      <c r="M35" s="31">
-        <v>0</v>
-      </c>
-      <c r="N35" s="34">
+      <c r="M35" s="29">
+        <v>0</v>
+      </c>
+      <c r="N35" s="32">
         <v>96.533333333333346</v>
       </c>
-      <c r="O35" s="34">
+      <c r="O35" s="32">
         <v>46.75</v>
       </c>
-      <c r="P35" s="34">
+      <c r="P35" s="32">
         <v>59.133333333333333</v>
       </c>
       <c r="W35">
         <v>8.66325026666666</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36" s="31" t="s">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A36" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="32">
+      <c r="B36" s="30">
         <v>45049</v>
       </c>
-      <c r="C36" s="31">
-        <v>0</v>
-      </c>
-      <c r="D36" s="31">
+      <c r="C36" s="29">
+        <v>0</v>
+      </c>
+      <c r="D36" s="29">
         <v>90.6</v>
       </c>
-      <c r="E36" s="31">
+      <c r="E36" s="29">
         <v>90.7</v>
       </c>
-      <c r="F36" s="31">
+      <c r="F36" s="29">
         <v>50.29</v>
       </c>
-      <c r="G36" s="31" t="s">
+      <c r="G36" s="29" t="s">
         <v>76</v>
       </c>
       <c r="H36" t="s">
         <v>74</v>
       </c>
-      <c r="I36" s="33" t="s">
+      <c r="I36" s="31" t="s">
         <v>349</v>
       </c>
-      <c r="J36" s="48" t="s">
+      <c r="J36" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="K36" s="49">
+      <c r="K36" s="47">
         <v>45040.708333333336</v>
       </c>
-      <c r="L36" s="31">
+      <c r="L36" s="29">
         <v>253</v>
       </c>
-      <c r="M36" s="31">
-        <v>0</v>
-      </c>
-      <c r="N36" s="34">
+      <c r="M36" s="29">
+        <v>0</v>
+      </c>
+      <c r="N36" s="32">
         <v>96.2</v>
       </c>
-      <c r="O36" s="34">
+      <c r="O36" s="32">
         <v>27.12</v>
       </c>
-      <c r="P36" s="34">
+      <c r="P36" s="32">
         <v>48.05</v>
       </c>
       <c r="W36">
         <v>10.072311133333301</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A37" s="31" t="s">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A37" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="B37" s="32">
+      <c r="B37" s="30">
         <v>45051</v>
       </c>
-      <c r="C37" s="31">
-        <v>0</v>
-      </c>
-      <c r="D37" s="31">
+      <c r="C37" s="29">
+        <v>0</v>
+      </c>
+      <c r="D37" s="29">
         <v>96.8</v>
       </c>
-      <c r="E37" s="31">
+      <c r="E37" s="29">
         <v>27.45</v>
       </c>
-      <c r="F37" s="31">
+      <c r="F37" s="29">
         <v>46.41</v>
       </c>
-      <c r="G37" s="31" t="s">
+      <c r="G37" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="I37" s="33" t="s">
+      <c r="I37" s="31" t="s">
         <v>350</v>
       </c>
-      <c r="J37" s="48" t="s">
+      <c r="J37" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="K37" s="49">
+      <c r="K37" s="47">
         <v>45040.916666666664</v>
       </c>
-      <c r="L37" s="31">
+      <c r="L37" s="29">
         <v>269</v>
       </c>
-      <c r="M37" s="31">
-        <v>0</v>
-      </c>
-      <c r="N37" s="34">
+      <c r="M37" s="29">
+        <v>0</v>
+      </c>
+      <c r="N37" s="32">
         <v>97.05</v>
       </c>
-      <c r="O37" s="34">
+      <c r="O37" s="32">
         <v>14.59</v>
       </c>
-      <c r="P37" s="34">
+      <c r="P37" s="32">
         <v>25.344999999999999</v>
       </c>
       <c r="W37">
         <v>6.9584305310000003</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="31" t="s">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A38" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="30">
         <v>45051</v>
       </c>
-      <c r="C38" s="31">
-        <v>0</v>
-      </c>
-      <c r="D38" s="31">
+      <c r="C38" s="29">
+        <v>0</v>
+      </c>
+      <c r="D38" s="29">
         <v>96.4</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="29">
         <v>34.18</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="29">
         <v>54.43</v>
       </c>
-      <c r="G38" s="31" t="s">
+      <c r="G38" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="I38" s="29" t="s">
+      <c r="I38" s="1" t="s">
         <v>351</v>
       </c>
       <c r="J38" s="2" t="s">
@@ -11976,36 +11969,36 @@
       <c r="P38" s="22">
         <v>0</v>
       </c>
-      <c r="Q38" s="59">
+      <c r="Q38" s="49">
         <v>7.3385368</v>
       </c>
       <c r="W38">
         <v>6.6294694666666603</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A39" s="31" t="s">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A39" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="30">
         <v>45051</v>
       </c>
-      <c r="C39" s="31">
-        <v>0</v>
-      </c>
-      <c r="D39" s="31">
+      <c r="C39" s="29">
+        <v>0</v>
+      </c>
+      <c r="D39" s="29">
         <v>97</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="29">
         <v>23.69</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="29">
         <v>42.18</v>
       </c>
-      <c r="G39" s="31" t="s">
+      <c r="G39" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="I39" s="29" t="s">
+      <c r="I39" s="1" t="s">
         <v>352</v>
       </c>
       <c r="J39" s="2" t="s">
@@ -12036,29 +12029,29 @@
         <v>5.5344294666666602</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A40" s="31" t="s">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A40" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="B40" s="38">
+      <c r="B40" s="36">
         <v>45051</v>
       </c>
-      <c r="C40" s="31">
-        <v>0</v>
-      </c>
-      <c r="D40" s="31">
+      <c r="C40" s="29">
+        <v>0</v>
+      </c>
+      <c r="D40" s="29">
         <v>96.8</v>
       </c>
-      <c r="E40" s="31">
+      <c r="E40" s="29">
         <v>23.58</v>
       </c>
-      <c r="F40" s="31">
+      <c r="F40" s="29">
         <v>39.93</v>
       </c>
-      <c r="G40" s="31" t="s">
+      <c r="G40" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="I40" s="29" t="s">
+      <c r="I40" s="1" t="s">
         <v>353</v>
       </c>
       <c r="J40" s="7" t="s">
@@ -12089,29 +12082,29 @@
         <v>5.7944035333333304</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A41" s="31" t="s">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A41" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="B41" s="32">
+      <c r="B41" s="30">
         <v>45051</v>
       </c>
-      <c r="C41" s="31">
-        <v>0</v>
-      </c>
-      <c r="D41" s="31">
+      <c r="C41" s="29">
+        <v>0</v>
+      </c>
+      <c r="D41" s="29">
         <v>96.7</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="29">
         <v>29.56</v>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="29">
         <v>50.47</v>
       </c>
-      <c r="G41" s="31" t="s">
+      <c r="G41" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="I41" s="29" t="s">
+      <c r="I41" s="1" t="s">
         <v>354</v>
       </c>
       <c r="J41" s="7" t="s">
@@ -12142,7 +12135,7 @@
         <v>6.8484111333333297</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>87</v>
       </c>
@@ -12164,7 +12157,7 @@
       <c r="G42" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I42" s="29" t="s">
+      <c r="I42" s="1" t="s">
         <v>355</v>
       </c>
       <c r="J42" s="7" t="s">
@@ -12195,7 +12188,7 @@
         <v>8.7752321066666603</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>88</v>
       </c>
@@ -12217,7 +12210,7 @@
       <c r="G43" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I43" s="29" t="s">
+      <c r="I43" s="1" t="s">
         <v>356</v>
       </c>
       <c r="J43" s="5" t="s">
@@ -12248,7 +12241,7 @@
         <v>8.5553027999999998</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>89</v>
       </c>
@@ -12270,7 +12263,7 @@
       <c r="G44" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I44" s="29" t="s">
+      <c r="I44" s="1" t="s">
         <v>357</v>
       </c>
       <c r="J44" s="7" t="s">
@@ -12301,7 +12294,7 @@
         <v>8.3964748666666598</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>90</v>
       </c>
@@ -12323,7 +12316,7 @@
       <c r="G45" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I45" s="29" t="s">
+      <c r="I45" s="1" t="s">
         <v>358</v>
       </c>
       <c r="J45" s="7" t="s">
@@ -12354,29 +12347,29 @@
         <v>11.483500266666599</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="31" t="s">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A46" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="32">
+      <c r="B46" s="30">
         <v>45048</v>
       </c>
-      <c r="C46" s="31">
-        <v>0</v>
-      </c>
-      <c r="D46" s="31">
+      <c r="C46" s="29">
+        <v>0</v>
+      </c>
+      <c r="D46" s="29">
         <v>95.6</v>
       </c>
-      <c r="E46" s="31">
+      <c r="E46" s="29">
         <v>64.14</v>
       </c>
-      <c r="F46" s="31">
+      <c r="F46" s="29">
         <v>87.02</v>
       </c>
-      <c r="G46" s="31" t="s">
+      <c r="G46" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="I46" s="29" t="s">
+      <c r="I46" s="1" t="s">
         <v>359</v>
       </c>
       <c r="J46" s="2" t="s">
@@ -12407,7 +12400,7 @@
         <v>5.4046995333333303</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>95</v>
       </c>
@@ -12429,7 +12422,7 @@
       <c r="G47" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I47" s="29" t="s">
+      <c r="I47" s="1" t="s">
         <v>360</v>
       </c>
       <c r="J47" s="5" t="s">
@@ -12456,33 +12449,33 @@
       <c r="Q47">
         <v>8.5553027999999998</v>
       </c>
-      <c r="W47" s="59">
+      <c r="W47" s="49">
         <v>5.62346873333333</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="31" t="s">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A48" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="B48" s="32">
+      <c r="B48" s="30">
         <v>45050</v>
       </c>
-      <c r="C48" s="31">
-        <v>0</v>
-      </c>
-      <c r="D48" s="31">
+      <c r="C48" s="29">
+        <v>0</v>
+      </c>
+      <c r="D48" s="29">
         <v>95.7</v>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="29">
         <v>26.28</v>
       </c>
-      <c r="F48" s="31">
+      <c r="F48" s="29">
         <v>36.200000000000003</v>
       </c>
-      <c r="G48" s="31" t="s">
+      <c r="G48" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="I48" s="29" t="s">
+      <c r="I48" s="1" t="s">
         <v>361</v>
       </c>
       <c r="J48" s="7" t="s">
@@ -12513,7 +12506,7 @@
         <v>6.59702113333333</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>101</v>
       </c>
@@ -12535,7 +12528,7 @@
       <c r="G49" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I49" s="29" t="s">
+      <c r="I49" s="1" t="s">
         <v>362</v>
       </c>
       <c r="J49" s="5" t="s">
@@ -12566,29 +12559,29 @@
         <v>4.8982727333333296</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A50" s="31" t="s">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A50" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="B50" s="32">
+      <c r="B50" s="30">
         <v>45050</v>
       </c>
-      <c r="C50" s="31">
-        <v>0</v>
-      </c>
-      <c r="D50" s="31">
+      <c r="C50" s="29">
+        <v>0</v>
+      </c>
+      <c r="D50" s="29">
         <v>96.6</v>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="29">
         <v>35.26</v>
       </c>
-      <c r="F50" s="31">
+      <c r="F50" s="29">
         <v>133.34</v>
       </c>
-      <c r="G50" s="31" t="s">
+      <c r="G50" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="I50" s="29" t="s">
+      <c r="I50" s="1" t="s">
         <v>363</v>
       </c>
       <c r="J50" s="2" t="s">
@@ -12619,79 +12612,79 @@
         <v>12.434267999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A51" s="31" t="s">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A51" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="B51" s="32">
+      <c r="B51" s="30">
         <v>45051</v>
       </c>
-      <c r="C51" s="31">
-        <v>0</v>
-      </c>
-      <c r="D51" s="31">
+      <c r="C51" s="29">
+        <v>0</v>
+      </c>
+      <c r="D51" s="29">
         <v>95.1</v>
       </c>
-      <c r="E51" s="31">
+      <c r="E51" s="29">
         <v>99.54</v>
       </c>
-      <c r="F51" s="31">
+      <c r="F51" s="29">
         <v>113.11</v>
       </c>
-      <c r="G51" s="31" t="s">
+      <c r="G51" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="I51" s="33" t="s">
+      <c r="I51" s="31" t="s">
         <v>364</v>
       </c>
-      <c r="J51" s="50" t="s">
+      <c r="J51" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="K51" s="32">
+      <c r="K51" s="30">
         <v>45044.666666666664</v>
       </c>
-      <c r="L51" s="31">
+      <c r="L51" s="29">
         <v>291</v>
       </c>
-      <c r="M51" s="31">
-        <v>0</v>
-      </c>
-      <c r="N51" s="34">
+      <c r="M51" s="29">
+        <v>0</v>
+      </c>
+      <c r="N51" s="32">
         <v>96.825000000000003</v>
       </c>
-      <c r="O51" s="34">
+      <c r="O51" s="32">
         <v>56.017499999999998</v>
       </c>
-      <c r="P51" s="34">
+      <c r="P51" s="32">
         <v>47.98</v>
       </c>
       <c r="W51">
         <v>8.70769666666666</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A52" s="31" t="s">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A52" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="B52" s="32">
+      <c r="B52" s="30">
         <v>45051</v>
       </c>
-      <c r="C52" s="31">
-        <v>0</v>
-      </c>
-      <c r="D52" s="31">
+      <c r="C52" s="29">
+        <v>0</v>
+      </c>
+      <c r="D52" s="29">
         <v>96.2</v>
       </c>
-      <c r="E52" s="31">
+      <c r="E52" s="29">
         <v>40.119999999999997</v>
       </c>
-      <c r="F52" s="31">
+      <c r="F52" s="29">
         <v>93.39</v>
       </c>
-      <c r="G52" s="31" t="s">
+      <c r="G52" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="I52" s="29" t="s">
+      <c r="I52" s="1" t="s">
         <v>365</v>
       </c>
       <c r="J52" s="8" t="s">
@@ -12715,14 +12708,14 @@
       <c r="P52" s="22">
         <v>0</v>
       </c>
-      <c r="Q52" s="59">
+      <c r="Q52" s="49">
         <v>5.62346873333333</v>
       </c>
       <c r="W52">
         <v>10.258584000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>113</v>
       </c>
@@ -12744,7 +12737,7 @@
       <c r="G53" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I53" s="29" t="s">
+      <c r="I53" s="1" t="s">
         <v>366</v>
       </c>
       <c r="J53" s="8" t="s">
@@ -12775,29 +12768,29 @@
         <v>7.5019323999999896</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A54" s="31" t="s">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A54" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="B54" s="32">
+      <c r="B54" s="30">
         <v>45050</v>
       </c>
-      <c r="C54" s="31">
-        <v>0</v>
-      </c>
-      <c r="D54" s="31">
+      <c r="C54" s="29">
+        <v>0</v>
+      </c>
+      <c r="D54" s="29">
         <v>95.5</v>
       </c>
-      <c r="E54" s="31">
+      <c r="E54" s="29">
         <v>72.78</v>
       </c>
-      <c r="F54" s="31">
+      <c r="F54" s="29">
         <v>79.66</v>
       </c>
-      <c r="G54" s="31" t="s">
+      <c r="G54" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="I54" s="29" t="s">
+      <c r="I54" s="1" t="s">
         <v>367</v>
       </c>
       <c r="J54" s="2" t="s">
@@ -12828,7 +12821,7 @@
         <v>20.852958666666598</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>123</v>
       </c>
@@ -12850,7 +12843,7 @@
       <c r="G55" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I55" s="29" t="s">
+      <c r="I55" s="1" t="s">
         <v>368</v>
       </c>
       <c r="J55" s="2" t="s">
@@ -12881,7 +12874,7 @@
         <v>12.526063343999899</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>106</v>
       </c>
@@ -12903,7 +12896,7 @@
       <c r="G56" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I56" s="29" t="s">
+      <c r="I56" s="1" t="s">
         <v>369</v>
       </c>
       <c r="J56" s="5" t="s">
@@ -12934,29 +12927,29 @@
         <v>9.3400750666666603</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A57" s="31" t="s">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A57" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="B57" s="32">
+      <c r="B57" s="30">
         <v>45046</v>
       </c>
-      <c r="C57" s="31">
-        <v>0</v>
-      </c>
-      <c r="D57" s="31">
+      <c r="C57" s="29">
+        <v>0</v>
+      </c>
+      <c r="D57" s="29">
         <v>96.7</v>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="29">
         <v>43.66</v>
       </c>
-      <c r="F57" s="31">
+      <c r="F57" s="29">
         <v>79.88</v>
       </c>
-      <c r="G57" s="31" t="s">
+      <c r="G57" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="I57" s="29" t="s">
+      <c r="I57" s="1" t="s">
         <v>370</v>
       </c>
       <c r="J57" s="5" t="s">
@@ -12987,7 +12980,7 @@
         <v>12.602335333333301</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>81</v>
       </c>
@@ -13009,7 +13002,7 @@
       <c r="G58" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I58" s="29" t="s">
+      <c r="I58" s="1" t="s">
         <v>371</v>
       </c>
       <c r="J58" s="7" t="s">
@@ -13040,7 +13033,7 @@
         <v>20.458221333333299</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>115</v>
       </c>
@@ -13062,35 +13055,35 @@
       <c r="G59" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I59" s="33" t="s">
+      <c r="I59" s="31" t="s">
         <v>372</v>
       </c>
-      <c r="J59" s="31" t="s">
+      <c r="J59" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="K59" s="32">
+      <c r="K59" s="30">
         <v>45046.541666666664</v>
       </c>
-      <c r="L59" s="31">
+      <c r="L59" s="29">
         <v>309</v>
       </c>
-      <c r="M59" s="31">
-        <v>0</v>
-      </c>
-      <c r="N59" s="34">
+      <c r="M59" s="29">
+        <v>0</v>
+      </c>
+      <c r="N59" s="32">
         <v>96.7</v>
       </c>
-      <c r="O59" s="34">
+      <c r="O59" s="32">
         <v>43.66</v>
       </c>
-      <c r="P59" s="34">
+      <c r="P59" s="32">
         <v>79.88</v>
       </c>
       <c r="W59">
         <v>12.6200733333333</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>133</v>
       </c>
@@ -13112,35 +13105,35 @@
       <c r="G60" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I60" s="33" t="s">
+      <c r="I60" s="31" t="s">
         <v>373</v>
       </c>
-      <c r="J60" s="48" t="s">
+      <c r="J60" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="K60" s="49">
+      <c r="K60" s="47">
         <v>45046.75</v>
       </c>
-      <c r="L60" s="31">
+      <c r="L60" s="29">
         <v>310</v>
       </c>
-      <c r="M60" s="31">
-        <v>0</v>
-      </c>
-      <c r="N60" s="34">
+      <c r="M60" s="29">
+        <v>0</v>
+      </c>
+      <c r="N60" s="32">
         <v>0.9</v>
       </c>
-      <c r="O60" s="34">
+      <c r="O60" s="32">
         <v>85.5</v>
       </c>
-      <c r="P60" s="34">
+      <c r="P60" s="32">
         <v>53.17</v>
       </c>
       <c r="W60">
         <v>8.4514112000000008</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>140</v>
       </c>
@@ -13162,7 +13155,7 @@
       <c r="G61" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I61" s="29" t="s">
+      <c r="I61" s="1" t="s">
         <v>374</v>
       </c>
       <c r="J61" s="7" t="s">
@@ -13193,7 +13186,7 @@
         <v>10.38581286</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>102</v>
       </c>
@@ -13215,7 +13208,7 @@
       <c r="G62" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I62" s="29" t="s">
+      <c r="I62" s="1" t="s">
         <v>375</v>
       </c>
       <c r="J62" s="2" t="s">
@@ -13246,7 +13239,7 @@
         <v>8.9650455999999998</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>51</v>
       </c>
@@ -13268,7 +13261,7 @@
       <c r="G63" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I63" s="29" t="s">
+      <c r="I63" s="1" t="s">
         <v>376</v>
       </c>
       <c r="J63" s="2" t="s">
@@ -13299,7 +13292,7 @@
         <v>12.044964</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>95</v>
       </c>
@@ -13321,7 +13314,7 @@
       <c r="G64" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I64" s="29" t="s">
+      <c r="I64" s="1" t="s">
         <v>377</v>
       </c>
       <c r="J64" s="7" t="s">
@@ -13352,7 +13345,7 @@
         <v>11.1430651333333</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>142</v>
       </c>
@@ -13374,35 +13367,35 @@
       <c r="G65" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I65" s="33" t="s">
+      <c r="I65" s="31" t="s">
         <v>378</v>
       </c>
-      <c r="J65" s="31" t="s">
+      <c r="J65" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="K65" s="32">
+      <c r="K65" s="30">
         <v>45047.833333333336</v>
       </c>
-      <c r="L65" s="31">
+      <c r="L65" s="29">
         <v>328</v>
       </c>
-      <c r="M65" s="31">
-        <v>0</v>
-      </c>
-      <c r="N65" s="34">
+      <c r="M65" s="29">
+        <v>0</v>
+      </c>
+      <c r="N65" s="32">
         <v>95.6</v>
       </c>
-      <c r="O65" s="34">
+      <c r="O65" s="32">
         <v>64.14</v>
       </c>
-      <c r="P65" s="34">
+      <c r="P65" s="32">
         <v>87.02</v>
       </c>
       <c r="W65">
         <v>7.3809661999999996</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>9</v>
       </c>
@@ -13424,7 +13417,7 @@
       <c r="G66" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I66" s="29" t="s">
+      <c r="I66" s="1" t="s">
         <v>379</v>
       </c>
       <c r="J66" s="2" t="s">
@@ -13455,29 +13448,29 @@
         <v>10.366192399999999</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A67" s="48" t="s">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A67" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="B67" s="49">
+      <c r="B67" s="47">
         <v>45040</v>
       </c>
-      <c r="C67" s="31">
-        <v>0</v>
-      </c>
-      <c r="D67" s="31">
+      <c r="C67" s="29">
+        <v>0</v>
+      </c>
+      <c r="D67" s="29">
         <v>96.2</v>
       </c>
-      <c r="E67" s="31">
+      <c r="E67" s="29">
         <v>27.12</v>
       </c>
-      <c r="F67" s="31">
+      <c r="F67" s="29">
         <v>48.05</v>
       </c>
-      <c r="G67" s="31" t="s">
+      <c r="G67" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="I67" s="29" t="s">
+      <c r="I67" s="1" t="s">
         <v>380</v>
       </c>
       <c r="J67" s="2" t="s">
@@ -13508,29 +13501,29 @@
         <v>4.5956702079999996</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A68" s="48" t="s">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A68" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B68" s="49">
+      <c r="B68" s="47">
         <v>45036</v>
       </c>
-      <c r="C68" s="31">
-        <v>0</v>
-      </c>
-      <c r="D68" s="31">
+      <c r="C68" s="29">
+        <v>0</v>
+      </c>
+      <c r="D68" s="29">
         <v>97</v>
       </c>
-      <c r="E68" s="31">
+      <c r="E68" s="29">
         <v>24.91</v>
       </c>
-      <c r="F68" s="31">
+      <c r="F68" s="29">
         <v>58.21</v>
       </c>
-      <c r="G68" s="31" t="s">
+      <c r="G68" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="I68" s="29" t="s">
+      <c r="I68" s="1" t="s">
         <v>381</v>
       </c>
       <c r="J68" s="5" t="s">
@@ -13561,29 +13554,29 @@
         <v>9.1948653333333308</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A69" s="48" t="s">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A69" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="B69" s="49">
+      <c r="B69" s="47">
         <v>45035</v>
       </c>
-      <c r="C69" s="31">
-        <v>0</v>
-      </c>
-      <c r="D69" s="31">
+      <c r="C69" s="29">
+        <v>0</v>
+      </c>
+      <c r="D69" s="29">
         <v>96.9</v>
       </c>
-      <c r="E69" s="31">
+      <c r="E69" s="29">
         <v>21.92</v>
       </c>
-      <c r="F69" s="31">
+      <c r="F69" s="29">
         <v>38.29</v>
       </c>
-      <c r="G69" s="31" t="s">
+      <c r="G69" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="I69" s="29" t="s">
+      <c r="I69" s="1" t="s">
         <v>382</v>
       </c>
       <c r="J69" s="2" t="s">
@@ -13611,29 +13604,29 @@
         <v>10.38581286</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A70" s="48" t="s">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A70" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="B70" s="49">
+      <c r="B70" s="47">
         <v>45035</v>
       </c>
-      <c r="C70" s="31">
-        <v>0</v>
-      </c>
-      <c r="D70" s="31">
+      <c r="C70" s="29">
+        <v>0</v>
+      </c>
+      <c r="D70" s="29">
         <v>96.7</v>
       </c>
-      <c r="E70" s="31">
+      <c r="E70" s="29">
         <v>22.8</v>
       </c>
-      <c r="F70" s="31">
+      <c r="F70" s="29">
         <v>39.340000000000003</v>
       </c>
-      <c r="G70" s="31" t="s">
+      <c r="G70" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="I70" s="29" t="s">
+      <c r="I70" s="1" t="s">
         <v>383</v>
       </c>
       <c r="J70" s="2" t="s">
@@ -13661,7 +13654,7 @@
         <v>8.9650455999999998</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
         <v>142</v>
       </c>
@@ -13683,79 +13676,79 @@
       <c r="G71" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I71" s="33" t="s">
+      <c r="I71" s="31" t="s">
         <v>384</v>
       </c>
-      <c r="J71" s="31" t="s">
+      <c r="J71" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="K71" s="32">
+      <c r="K71" s="30">
         <v>45049.583333333336</v>
       </c>
-      <c r="L71" s="31">
+      <c r="L71" s="29">
         <v>334</v>
       </c>
-      <c r="M71" s="31">
-        <v>0</v>
-      </c>
-      <c r="N71" s="34">
+      <c r="M71" s="29">
+        <v>0</v>
+      </c>
+      <c r="N71" s="32">
         <v>96.4</v>
       </c>
-      <c r="O71" s="34">
+      <c r="O71" s="32">
         <v>39.619999999999997</v>
       </c>
-      <c r="P71" s="34">
+      <c r="P71" s="32">
         <v>54.92</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A72" s="48" t="s">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A72" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="B72" s="49">
+      <c r="B72" s="47">
         <v>45046</v>
       </c>
-      <c r="C72" s="31">
-        <v>0</v>
-      </c>
-      <c r="D72" s="31">
+      <c r="C72" s="29">
+        <v>0</v>
+      </c>
+      <c r="D72" s="29">
         <v>0.9</v>
       </c>
-      <c r="E72" s="31">
+      <c r="E72" s="29">
         <v>85.5</v>
       </c>
-      <c r="F72" s="31">
+      <c r="F72" s="29">
         <v>53.17</v>
       </c>
-      <c r="G72" s="31" t="s">
+      <c r="G72" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="I72" s="33" t="s">
+      <c r="I72" s="31" t="s">
         <v>385</v>
       </c>
-      <c r="J72" s="31" t="s">
+      <c r="J72" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="K72" s="32">
+      <c r="K72" s="30">
         <v>45049.833333333336</v>
       </c>
-      <c r="L72" s="31">
+      <c r="L72" s="29">
         <v>335</v>
       </c>
-      <c r="M72" s="31">
-        <v>0</v>
-      </c>
-      <c r="N72" s="34">
+      <c r="M72" s="29">
+        <v>0</v>
+      </c>
+      <c r="N72" s="32">
         <v>91.033333333333346</v>
       </c>
-      <c r="O72" s="34">
+      <c r="O72" s="32">
         <v>87.100000000000009</v>
       </c>
-      <c r="P72" s="34">
+      <c r="P72" s="32">
         <v>49.949999999999996</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
         <v>89</v>
       </c>
@@ -13777,7 +13770,7 @@
       <c r="G73" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I73" s="29" t="s">
+      <c r="I73" s="1" t="s">
         <v>386</v>
       </c>
       <c r="J73" s="7" t="s">
@@ -13805,7 +13798,7 @@
         <v>12.044964</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
         <v>81</v>
       </c>
@@ -13827,54 +13820,54 @@
       <c r="G74" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I74" s="33" t="s">
+      <c r="I74" s="31" t="s">
         <v>387</v>
       </c>
-      <c r="J74" s="31" t="s">
+      <c r="J74" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="K74" s="32">
+      <c r="K74" s="30">
         <v>45050.083333333336</v>
       </c>
-      <c r="L74" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="M74" s="31">
-        <v>0</v>
-      </c>
-      <c r="N74" s="34">
+      <c r="L74" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="M74" s="29">
+        <v>0</v>
+      </c>
+      <c r="N74" s="32">
         <v>95.7</v>
       </c>
-      <c r="O74" s="34">
+      <c r="O74" s="32">
         <v>26.28</v>
       </c>
-      <c r="P74" s="34">
+      <c r="P74" s="32">
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A75" s="48" t="s">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A75" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="B75" s="49">
+      <c r="B75" s="47">
         <v>45040</v>
       </c>
-      <c r="C75" s="31">
-        <v>0</v>
-      </c>
-      <c r="D75" s="31">
+      <c r="C75" s="29">
+        <v>0</v>
+      </c>
+      <c r="D75" s="29">
         <v>97.1</v>
       </c>
-      <c r="E75" s="31">
+      <c r="E75" s="29">
         <v>13.73</v>
       </c>
-      <c r="F75" s="31">
+      <c r="F75" s="29">
         <v>22.85</v>
       </c>
-      <c r="G75" s="31" t="s">
+      <c r="G75" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="I75" s="29" t="s">
+      <c r="I75" s="1" t="s">
         <v>388</v>
       </c>
       <c r="J75" s="2" t="s">
@@ -13902,29 +13895,29 @@
         <v>11.1430651333333</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A76" s="47" t="s">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A76" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="49">
+      <c r="B76" s="47">
         <v>45040</v>
       </c>
-      <c r="C76" s="31">
-        <v>0</v>
-      </c>
-      <c r="D76" s="31">
+      <c r="C76" s="29">
+        <v>0</v>
+      </c>
+      <c r="D76" s="29">
         <v>97</v>
       </c>
-      <c r="E76" s="31">
+      <c r="E76" s="29">
         <v>15.45</v>
       </c>
-      <c r="F76" s="31">
+      <c r="F76" s="29">
         <v>27.84</v>
       </c>
-      <c r="G76" s="31" t="s">
+      <c r="G76" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="I76" s="29" t="s">
+      <c r="I76" s="1" t="s">
         <v>389</v>
       </c>
       <c r="J76" s="2" t="s">
@@ -13952,54 +13945,54 @@
         <v>7.3809661999999996</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A77" s="47" t="s">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A77" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="B77" s="49">
+      <c r="B77" s="47">
         <v>45036</v>
       </c>
-      <c r="C77" s="31">
-        <v>0</v>
-      </c>
-      <c r="D77" s="31">
+      <c r="C77" s="29">
+        <v>0</v>
+      </c>
+      <c r="D77" s="29">
         <v>96.8</v>
       </c>
-      <c r="E77" s="31">
+      <c r="E77" s="29">
         <v>30.83</v>
       </c>
-      <c r="F77" s="31">
+      <c r="F77" s="29">
         <v>52.1</v>
       </c>
-      <c r="G77" s="31" t="s">
+      <c r="G77" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="I77" s="33" t="s">
+      <c r="I77" s="31" t="s">
         <v>390</v>
       </c>
-      <c r="J77" s="31" t="s">
+      <c r="J77" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="K77" s="32">
+      <c r="K77" s="30">
         <v>45050.458333333336</v>
       </c>
-      <c r="L77" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="M77" s="31">
-        <v>0</v>
-      </c>
-      <c r="N77" s="34">
+      <c r="L77" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="M77" s="29">
+        <v>0</v>
+      </c>
+      <c r="N77" s="32">
         <v>96.6</v>
       </c>
-      <c r="O77" s="34">
+      <c r="O77" s="32">
         <v>35.26</v>
       </c>
-      <c r="P77" s="34">
+      <c r="P77" s="32">
         <v>133.34</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>102</v>
       </c>
@@ -14021,7 +14014,7 @@
       <c r="G78" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I78" s="29" t="s">
+      <c r="I78" s="1" t="s">
         <v>391</v>
       </c>
       <c r="J78" s="2" t="s">
@@ -14049,7 +14042,7 @@
         <v>10.366192399999999</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>51</v>
       </c>
@@ -14071,32 +14064,32 @@
       <c r="G79" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I79" s="33" t="s">
+      <c r="I79" s="31" t="s">
         <v>392</v>
       </c>
-      <c r="J79" s="31" t="s">
+      <c r="J79" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="K79" s="32">
+      <c r="K79" s="30">
         <v>45050.708333333336</v>
       </c>
-      <c r="L79" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="M79" s="31">
-        <v>0</v>
-      </c>
-      <c r="N79" s="34">
+      <c r="L79" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="M79" s="29">
+        <v>0</v>
+      </c>
+      <c r="N79" s="32">
         <v>95.5</v>
       </c>
-      <c r="O79" s="34">
+      <c r="O79" s="32">
         <v>72.78</v>
       </c>
-      <c r="P79" s="34">
+      <c r="P79" s="32">
         <v>79.66</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>113</v>
       </c>
@@ -14118,32 +14111,32 @@
       <c r="G80" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I80" s="33" t="s">
+      <c r="I80" s="31" t="s">
         <v>393</v>
       </c>
-      <c r="J80" s="31" t="s">
+      <c r="J80" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="K80" s="32">
+      <c r="K80" s="30">
         <v>45050.833333333336</v>
       </c>
-      <c r="L80" s="31">
+      <c r="L80" s="29">
         <v>338</v>
       </c>
-      <c r="M80" s="31">
-        <v>0</v>
-      </c>
-      <c r="N80" s="34">
+      <c r="M80" s="29">
+        <v>0</v>
+      </c>
+      <c r="N80" s="32">
         <v>96.2</v>
       </c>
-      <c r="O80" s="34">
+      <c r="O80" s="32">
         <v>25.16</v>
       </c>
-      <c r="P80" s="34">
+      <c r="P80" s="32">
         <v>30.57</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
         <v>95</v>
       </c>
@@ -14165,32 +14158,32 @@
       <c r="G81" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I81" s="33" t="s">
+      <c r="I81" s="31" t="s">
         <v>394</v>
       </c>
-      <c r="J81" s="31" t="s">
+      <c r="J81" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="K81" s="32">
+      <c r="K81" s="30">
         <v>45050.958333333336</v>
       </c>
-      <c r="L81" s="31">
+      <c r="L81" s="29">
         <v>339</v>
       </c>
-      <c r="M81" s="31">
-        <v>0</v>
-      </c>
-      <c r="N81" s="34">
+      <c r="M81" s="29">
+        <v>0</v>
+      </c>
+      <c r="N81" s="32">
         <v>97.066666666666663</v>
       </c>
-      <c r="O81" s="34">
+      <c r="O81" s="32">
         <v>15.186666666666667</v>
       </c>
-      <c r="P81" s="34">
+      <c r="P81" s="32">
         <v>26.823333333333334</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
         <v>95</v>
       </c>
@@ -14212,32 +14205,32 @@
       <c r="G82" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I82" s="33" t="s">
+      <c r="I82" s="31" t="s">
         <v>395</v>
       </c>
-      <c r="J82" s="31" t="s">
+      <c r="J82" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="K82" s="32">
+      <c r="K82" s="30">
         <v>45051.083333333336</v>
       </c>
-      <c r="L82" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="M82" s="31">
-        <v>0</v>
-      </c>
-      <c r="N82" s="34">
+      <c r="L82" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="M82" s="29">
+        <v>0</v>
+      </c>
+      <c r="N82" s="32">
         <v>95.1</v>
       </c>
-      <c r="O82" s="34">
+      <c r="O82" s="32">
         <v>99.54</v>
       </c>
-      <c r="P82" s="34">
+      <c r="P82" s="32">
         <v>113.11</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
         <v>104</v>
       </c>
@@ -14259,7 +14252,7 @@
       <c r="G83" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I83" s="29" t="s">
+      <c r="I83" s="1" t="s">
         <v>396</v>
       </c>
       <c r="J83" s="2" t="s">
@@ -14287,7 +14280,7 @@
         <v>4.5956702079999996</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
         <v>133</v>
       </c>
@@ -14309,32 +14302,32 @@
       <c r="G84" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I84" s="33" t="s">
+      <c r="I84" s="31" t="s">
         <v>397</v>
       </c>
-      <c r="J84" s="31" t="s">
+      <c r="J84" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="K84" s="32">
+      <c r="K84" s="30">
         <v>45051.333333333336</v>
       </c>
-      <c r="L84" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="M84" s="31">
-        <v>0</v>
-      </c>
-      <c r="N84" s="34">
+      <c r="L84" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="M84" s="29">
+        <v>0</v>
+      </c>
+      <c r="N84" s="32">
         <v>96.2</v>
       </c>
-      <c r="O84" s="34">
+      <c r="O84" s="32">
         <v>40.119999999999997</v>
       </c>
-      <c r="P84" s="34">
+      <c r="P84" s="32">
         <v>93.39</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
         <v>101</v>
       </c>
@@ -14356,32 +14349,32 @@
       <c r="G85" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I85" s="33" t="s">
+      <c r="I85" s="31" t="s">
         <v>398</v>
       </c>
-      <c r="J85" s="31" t="s">
+      <c r="J85" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="K85" s="32">
+      <c r="K85" s="30">
         <v>45051.458333333336</v>
       </c>
-      <c r="L85" s="31">
+      <c r="L85" s="29">
         <v>341</v>
       </c>
-      <c r="M85" s="31">
-        <v>0</v>
-      </c>
-      <c r="N85" s="34">
+      <c r="M85" s="29">
+        <v>0</v>
+      </c>
+      <c r="N85" s="32">
         <v>96.833333333333329</v>
       </c>
-      <c r="O85" s="34">
+      <c r="O85" s="32">
         <v>25.61</v>
       </c>
-      <c r="P85" s="34">
+      <c r="P85" s="32">
         <v>44.193333333333328</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
         <v>77</v>
       </c>
@@ -14403,7 +14396,7 @@
       <c r="G86" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I86" s="29" t="s">
+      <c r="I86" s="1" t="s">
         <v>399</v>
       </c>
       <c r="J86" s="2" t="s">
@@ -14431,7 +14424,7 @@
         <v>9.1948653333333308</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
         <v>10</v>
       </c>
@@ -14453,32 +14446,32 @@
       <c r="G87" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I87" s="33" t="s">
+      <c r="I87" s="31" t="s">
         <v>400</v>
       </c>
-      <c r="J87" s="31" t="s">
+      <c r="J87" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="K87" s="32">
+      <c r="K87" s="30">
         <v>45051.708333333336</v>
       </c>
-      <c r="L87" s="31">
+      <c r="L87" s="29">
         <v>342</v>
       </c>
-      <c r="M87" s="31">
-        <v>0</v>
-      </c>
-      <c r="N87" s="34">
+      <c r="M87" s="29">
+        <v>0</v>
+      </c>
+      <c r="N87" s="32">
         <v>96.6</v>
       </c>
-      <c r="O87" s="34">
+      <c r="O87" s="32">
         <v>30.814999999999998</v>
       </c>
-      <c r="P87" s="34">
+      <c r="P87" s="32">
         <v>50.42</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>8</v>
       </c>
@@ -14500,9 +14493,9 @@
       <c r="G88" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I88" s="29"/>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>155</v>
       </c>
@@ -14524,9 +14517,9 @@
       <c r="G89" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I89" s="29"/>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>90</v>
       </c>
@@ -14548,9 +14541,9 @@
       <c r="G90" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I90" s="29"/>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>156</v>
       </c>
@@ -14572,9 +14565,9 @@
       <c r="G91" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I91" s="29"/>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I91" s="1"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>123</v>
       </c>
@@ -14596,9 +14589,9 @@
       <c r="G92" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I92" s="29"/>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I92" s="1"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="8" t="s">
         <v>142</v>
       </c>
@@ -14620,105 +14613,105 @@
       <c r="G93" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I93" s="29"/>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94" s="50" t="s">
+      <c r="I93" s="1"/>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A94" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="B94" s="32">
+      <c r="B94" s="30">
         <v>45044</v>
       </c>
-      <c r="C94" s="31">
-        <v>0</v>
-      </c>
-      <c r="D94" s="31">
+      <c r="C94" s="29">
+        <v>0</v>
+      </c>
+      <c r="D94" s="29">
         <v>96.9</v>
       </c>
-      <c r="E94" s="31">
+      <c r="E94" s="29">
         <v>65.569999999999993</v>
       </c>
-      <c r="F94" s="31">
+      <c r="F94" s="29">
         <v>62.26</v>
       </c>
-      <c r="G94" s="31" t="s">
+      <c r="G94" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="I94" s="29"/>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A95" s="50" t="s">
+      <c r="I94" s="1"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A95" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="B95" s="32">
+      <c r="B95" s="30">
         <v>45044</v>
       </c>
-      <c r="C95" s="31">
-        <v>0</v>
-      </c>
-      <c r="D95" s="31">
+      <c r="C95" s="29">
+        <v>0</v>
+      </c>
+      <c r="D95" s="29">
         <v>98</v>
       </c>
-      <c r="E95" s="31">
-        <v>0</v>
-      </c>
-      <c r="F95" s="31">
-        <v>0</v>
-      </c>
-      <c r="G95" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I95" s="29"/>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96" s="50" t="s">
+      <c r="E95" s="29">
+        <v>0</v>
+      </c>
+      <c r="F95" s="29">
+        <v>0</v>
+      </c>
+      <c r="G95" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="I95" s="1"/>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A96" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="B96" s="32">
+      <c r="B96" s="30">
         <v>45044</v>
       </c>
-      <c r="C96" s="31">
-        <v>0</v>
-      </c>
-      <c r="D96" s="31">
+      <c r="C96" s="29">
+        <v>0</v>
+      </c>
+      <c r="D96" s="29">
         <v>96.4</v>
       </c>
-      <c r="E96" s="31">
+      <c r="E96" s="29">
         <v>74.290000000000006</v>
       </c>
-      <c r="F96" s="31">
+      <c r="F96" s="29">
         <v>64.09</v>
       </c>
-      <c r="G96" s="31" t="s">
+      <c r="G96" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="I96" s="29"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="50" t="s">
+      <c r="I96" s="1"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A97" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="B97" s="32">
+      <c r="B97" s="30">
         <v>45044</v>
       </c>
-      <c r="C97" s="31">
-        <v>0</v>
-      </c>
-      <c r="D97" s="31">
+      <c r="C97" s="29">
+        <v>0</v>
+      </c>
+      <c r="D97" s="29">
         <v>96</v>
       </c>
-      <c r="E97" s="31">
+      <c r="E97" s="29">
         <v>84.21</v>
       </c>
-      <c r="F97" s="31">
+      <c r="F97" s="29">
         <v>65.569999999999993</v>
       </c>
-      <c r="G97" s="31" t="s">
+      <c r="G97" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="I97" s="29"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I97" s="1"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="8" t="s">
         <v>99</v>
       </c>
@@ -14740,9 +14733,9 @@
       <c r="G98" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I98" s="29"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I98" s="1"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="8" t="s">
         <v>101</v>
       </c>
@@ -14764,201 +14757,201 @@
       <c r="G99" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I99" s="29"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="50" t="s">
+      <c r="I99" s="1"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="B100" s="32">
+      <c r="B100" s="30">
         <v>45033</v>
       </c>
-      <c r="C100" s="31">
-        <v>0</v>
-      </c>
-      <c r="D100" s="31">
+      <c r="C100" s="29">
+        <v>0</v>
+      </c>
+      <c r="D100" s="29">
         <v>97.2</v>
       </c>
-      <c r="E100" s="31">
+      <c r="E100" s="29">
         <v>83.26</v>
       </c>
-      <c r="F100" s="31">
+      <c r="F100" s="29">
         <v>101.8</v>
       </c>
-      <c r="G100" s="31" t="s">
+      <c r="G100" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="I100" s="29"/>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="31" t="s">
+      <c r="I100" s="1"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="B101" s="32">
+      <c r="B101" s="30">
         <v>45033</v>
       </c>
-      <c r="C101" s="31">
-        <v>0</v>
-      </c>
-      <c r="D101" s="31">
+      <c r="C101" s="29">
+        <v>0</v>
+      </c>
+      <c r="D101" s="29">
         <v>97.1</v>
       </c>
-      <c r="E101" s="31">
+      <c r="E101" s="29">
         <v>72.62</v>
       </c>
-      <c r="F101" s="31">
+      <c r="F101" s="29">
         <v>103.71</v>
       </c>
-      <c r="G101" s="31" t="s">
+      <c r="G101" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="I101" s="29"/>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="31" t="s">
+      <c r="I101" s="1"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="B102" s="32">
+      <c r="B102" s="30">
         <v>45033</v>
       </c>
-      <c r="C102" s="31">
-        <v>0</v>
-      </c>
-      <c r="D102" s="31">
+      <c r="C102" s="29">
+        <v>0</v>
+      </c>
+      <c r="D102" s="29">
         <v>97.1</v>
       </c>
-      <c r="E102" s="31">
+      <c r="E102" s="29">
         <v>67.23</v>
       </c>
-      <c r="F102" s="31">
+      <c r="F102" s="29">
         <v>80.28</v>
       </c>
-      <c r="G102" s="31" t="s">
+      <c r="G102" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="I102" s="29"/>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="31" t="s">
+      <c r="I102" s="1"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A103" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="B103" s="36">
+      <c r="B103" s="34">
         <v>45033</v>
       </c>
-      <c r="C103" s="31">
-        <v>0</v>
-      </c>
-      <c r="D103" s="31">
+      <c r="C103" s="29">
+        <v>0</v>
+      </c>
+      <c r="D103" s="29">
         <v>96.8</v>
       </c>
-      <c r="E103" s="31">
+      <c r="E103" s="29">
         <v>71.59</v>
       </c>
-      <c r="F103" s="31">
+      <c r="F103" s="29">
         <v>80.05</v>
       </c>
-      <c r="G103" s="31" t="s">
+      <c r="G103" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="I103" s="29"/>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="31" t="s">
+      <c r="I103" s="1"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A104" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="B104" s="36">
+      <c r="B104" s="34">
         <v>45034</v>
       </c>
-      <c r="C104" s="31">
-        <v>0</v>
-      </c>
-      <c r="D104" s="31">
+      <c r="C104" s="29">
+        <v>0</v>
+      </c>
+      <c r="D104" s="29">
         <v>96.9</v>
       </c>
-      <c r="E104" s="31">
+      <c r="E104" s="29">
         <v>49.12</v>
       </c>
-      <c r="F104" s="31">
+      <c r="F104" s="29">
         <v>61.74</v>
       </c>
-      <c r="G104" s="31" t="s">
+      <c r="G104" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="I104" s="29"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="31" t="s">
+      <c r="I104" s="1"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A105" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="B105" s="36">
+      <c r="B105" s="34">
         <v>45034</v>
       </c>
-      <c r="C105" s="31">
-        <v>0</v>
-      </c>
-      <c r="D105" s="31">
+      <c r="C105" s="29">
+        <v>0</v>
+      </c>
+      <c r="D105" s="29">
         <v>97</v>
       </c>
-      <c r="E105" s="31">
+      <c r="E105" s="29">
         <v>40.53</v>
       </c>
-      <c r="F105" s="31">
+      <c r="F105" s="29">
         <v>50.79</v>
       </c>
-      <c r="G105" s="31" t="s">
+      <c r="G105" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="I105" s="29"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="31" t="s">
+      <c r="I105" s="1"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A106" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="B106" s="36">
+      <c r="B106" s="34">
         <v>45034</v>
       </c>
-      <c r="C106" s="31">
-        <v>0</v>
-      </c>
-      <c r="D106" s="31">
+      <c r="C106" s="29">
+        <v>0</v>
+      </c>
+      <c r="D106" s="29">
         <v>96.9</v>
       </c>
-      <c r="E106" s="31">
+      <c r="E106" s="29">
         <v>50.66</v>
       </c>
-      <c r="F106" s="31">
+      <c r="F106" s="29">
         <v>60.92</v>
       </c>
-      <c r="G106" s="31" t="s">
+      <c r="G106" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="I106" s="29"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="31" t="s">
+      <c r="I106" s="1"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A107" s="29" t="s">
         <v>172</v>
       </c>
-      <c r="B107" s="36">
+      <c r="B107" s="34">
         <v>45034</v>
       </c>
-      <c r="C107" s="31">
-        <v>0</v>
-      </c>
-      <c r="D107" s="31">
+      <c r="C107" s="29">
+        <v>0</v>
+      </c>
+      <c r="D107" s="29">
         <v>96.8</v>
       </c>
-      <c r="E107" s="31">
+      <c r="E107" s="29">
         <v>55.27</v>
       </c>
-      <c r="F107" s="31">
+      <c r="F107" s="29">
         <v>61.39</v>
       </c>
-      <c r="G107" s="31" t="s">
+      <c r="G107" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="I107" s="29"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I107" s="1"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>133</v>
       </c>
@@ -14980,57 +14973,57 @@
       <c r="G108" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I108" s="29"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="31" t="s">
+      <c r="I108" s="1"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A109" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B109" s="36">
+      <c r="B109" s="34">
         <v>45033</v>
       </c>
-      <c r="C109" s="31">
-        <v>0</v>
-      </c>
-      <c r="D109" s="31">
+      <c r="C109" s="29">
+        <v>0</v>
+      </c>
+      <c r="D109" s="29">
         <v>93.6</v>
       </c>
-      <c r="E109" s="31">
+      <c r="E109" s="29">
         <v>103.03</v>
       </c>
-      <c r="F109" s="31">
+      <c r="F109" s="29">
         <v>71.760000000000005</v>
       </c>
-      <c r="G109" s="31" t="s">
+      <c r="G109" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="I109" s="29"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="31" t="s">
+      <c r="I109" s="1"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="B110" s="36">
+      <c r="B110" s="34">
         <v>45033</v>
       </c>
-      <c r="C110" s="31">
-        <v>0</v>
-      </c>
-      <c r="D110" s="31">
+      <c r="C110" s="29">
+        <v>0</v>
+      </c>
+      <c r="D110" s="29">
         <v>93.2</v>
       </c>
-      <c r="E110" s="31">
+      <c r="E110" s="29">
         <v>103.58</v>
       </c>
-      <c r="F110" s="31">
+      <c r="F110" s="29">
         <v>91.84</v>
       </c>
-      <c r="G110" s="31" t="s">
+      <c r="G110" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="I110" s="29"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I110" s="1"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>115</v>
       </c>
@@ -15052,9 +15045,9 @@
       <c r="G111" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I111" s="29"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I111" s="1"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>62</v>
       </c>
@@ -15076,9 +15069,9 @@
       <c r="G112" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I112" s="29"/>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I112" s="1"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>104</v>
       </c>
@@ -15100,153 +15093,153 @@
       <c r="G113" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I113" s="29"/>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="31" t="s">
+      <c r="I113" s="1"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A114" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="B114" s="36">
+      <c r="B114" s="34">
         <v>45040</v>
       </c>
-      <c r="C114" s="31">
-        <v>0</v>
-      </c>
-      <c r="D114" s="31">
+      <c r="C114" s="29">
+        <v>0</v>
+      </c>
+      <c r="D114" s="29">
         <v>97.3</v>
       </c>
-      <c r="E114" s="31">
+      <c r="E114" s="29">
         <v>70.010000000000005</v>
       </c>
-      <c r="F114" s="31">
+      <c r="F114" s="29">
         <v>73.97</v>
       </c>
-      <c r="G114" s="31" t="s">
+      <c r="G114" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="I114" s="29"/>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="31" t="s">
+      <c r="I114" s="1"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A115" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="B115" s="36">
+      <c r="B115" s="34">
         <v>45040</v>
       </c>
-      <c r="C115" s="31">
-        <v>0</v>
-      </c>
-      <c r="D115" s="31">
+      <c r="C115" s="29">
+        <v>0</v>
+      </c>
+      <c r="D115" s="29">
         <v>97.3</v>
       </c>
-      <c r="E115" s="31">
+      <c r="E115" s="29">
         <v>67.09</v>
       </c>
-      <c r="F115" s="31">
+      <c r="F115" s="29">
         <v>70.069999999999993</v>
       </c>
-      <c r="G115" s="31" t="s">
+      <c r="G115" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="I115" s="29"/>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="31" t="s">
+      <c r="I115" s="1"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A116" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="B116" s="36">
+      <c r="B116" s="34">
         <v>45040</v>
       </c>
-      <c r="C116" s="31">
-        <v>0</v>
-      </c>
-      <c r="D116" s="31">
+      <c r="C116" s="29">
+        <v>0</v>
+      </c>
+      <c r="D116" s="29">
         <v>97.3</v>
       </c>
-      <c r="E116" s="31">
+      <c r="E116" s="29">
         <v>62.66</v>
       </c>
-      <c r="F116" s="31">
+      <c r="F116" s="29">
         <v>65.38</v>
       </c>
-      <c r="G116" s="31" t="s">
+      <c r="G116" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="I116" s="29"/>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="31" t="s">
+      <c r="I116" s="1"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A117" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="B117" s="36">
+      <c r="B117" s="34">
         <v>45035</v>
       </c>
-      <c r="C117" s="31">
-        <v>0</v>
-      </c>
-      <c r="D117" s="31">
+      <c r="C117" s="29">
+        <v>0</v>
+      </c>
+      <c r="D117" s="29">
         <v>97.3</v>
       </c>
-      <c r="E117" s="31">
+      <c r="E117" s="29">
         <v>38.99</v>
       </c>
-      <c r="F117" s="31">
+      <c r="F117" s="29">
         <v>64.36</v>
       </c>
-      <c r="G117" s="31" t="s">
+      <c r="G117" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="I117" s="29"/>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="31" t="s">
+      <c r="I117" s="1"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A118" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="B118" s="36">
+      <c r="B118" s="34">
         <v>45035</v>
       </c>
-      <c r="C118" s="31">
-        <v>0</v>
-      </c>
-      <c r="D118" s="31">
+      <c r="C118" s="29">
+        <v>0</v>
+      </c>
+      <c r="D118" s="29">
         <v>97</v>
       </c>
-      <c r="E118" s="31">
+      <c r="E118" s="29">
         <v>40.549999999999997</v>
       </c>
-      <c r="F118" s="31">
+      <c r="F118" s="29">
         <v>59.68</v>
       </c>
-      <c r="G118" s="31" t="s">
+      <c r="G118" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="I118" s="29"/>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="31" t="s">
+      <c r="I118" s="1"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A119" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="B119" s="36">
+      <c r="B119" s="34">
         <v>45035</v>
       </c>
-      <c r="C119" s="31">
-        <v>0</v>
-      </c>
-      <c r="D119" s="31">
+      <c r="C119" s="29">
+        <v>0</v>
+      </c>
+      <c r="D119" s="29">
         <v>96.9</v>
       </c>
-      <c r="E119" s="31">
+      <c r="E119" s="29">
         <v>43.34</v>
       </c>
-      <c r="F119" s="31">
+      <c r="F119" s="29">
         <v>64.510000000000005</v>
       </c>
-      <c r="G119" s="31" t="s">
+      <c r="G119" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="I119" s="29"/>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I119" s="1"/>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>213</v>
       </c>
@@ -15268,129 +15261,129 @@
       <c r="G120" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I120" s="29"/>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="31" t="s">
+      <c r="I120" s="1"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A121" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="B121" s="36">
+      <c r="B121" s="34">
         <v>45035</v>
       </c>
-      <c r="C121" s="31">
-        <v>0</v>
-      </c>
-      <c r="D121" s="31">
+      <c r="C121" s="29">
+        <v>0</v>
+      </c>
+      <c r="D121" s="29">
         <v>96.9</v>
       </c>
-      <c r="E121" s="31">
+      <c r="E121" s="29">
         <v>40.33</v>
       </c>
-      <c r="F121" s="31">
+      <c r="F121" s="29">
         <v>53.86</v>
       </c>
-      <c r="G121" s="31" t="s">
+      <c r="G121" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="I121" s="29"/>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="31" t="s">
+      <c r="I121" s="1"/>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A122" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="B122" s="36">
+      <c r="B122" s="34">
         <v>45035</v>
       </c>
-      <c r="C122" s="31">
-        <v>0</v>
-      </c>
-      <c r="D122" s="31">
+      <c r="C122" s="29">
+        <v>0</v>
+      </c>
+      <c r="D122" s="29">
         <v>96.6</v>
       </c>
-      <c r="E122" s="31">
+      <c r="E122" s="29">
         <v>49.87</v>
       </c>
-      <c r="F122" s="31">
+      <c r="F122" s="29">
         <v>58.37</v>
       </c>
-      <c r="G122" s="31" t="s">
+      <c r="G122" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="I122" s="29"/>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="31" t="s">
+      <c r="I122" s="1"/>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A123" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="B123" s="36">
+      <c r="B123" s="34">
         <v>45035</v>
       </c>
-      <c r="C123" s="31">
-        <v>0</v>
-      </c>
-      <c r="D123" s="31">
+      <c r="C123" s="29">
+        <v>0</v>
+      </c>
+      <c r="D123" s="29">
         <v>96.4</v>
       </c>
-      <c r="E123" s="31">
+      <c r="E123" s="29">
         <v>52.54</v>
       </c>
-      <c r="F123" s="31">
+      <c r="F123" s="29">
         <v>59.24</v>
       </c>
-      <c r="G123" s="31" t="s">
+      <c r="G123" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="I123" s="29"/>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="31" t="s">
+      <c r="I123" s="1"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A124" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="B124" s="36">
+      <c r="B124" s="34">
         <v>45034</v>
       </c>
-      <c r="C124" s="31">
-        <v>0</v>
-      </c>
-      <c r="D124" s="31">
+      <c r="C124" s="29">
+        <v>0</v>
+      </c>
+      <c r="D124" s="29">
         <v>93.1</v>
       </c>
-      <c r="E124" s="31">
+      <c r="E124" s="29">
         <v>76.42</v>
       </c>
-      <c r="F124" s="31">
+      <c r="F124" s="29">
         <v>45.55</v>
       </c>
-      <c r="G124" s="31" t="s">
+      <c r="G124" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="I124" s="29"/>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="31" t="s">
+      <c r="I124" s="1"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A125" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="B125" s="36">
+      <c r="B125" s="34">
         <v>45034</v>
       </c>
-      <c r="C125" s="31">
-        <v>0</v>
-      </c>
-      <c r="D125" s="31">
+      <c r="C125" s="29">
+        <v>0</v>
+      </c>
+      <c r="D125" s="29">
         <v>92.8</v>
       </c>
-      <c r="E125" s="31">
+      <c r="E125" s="29">
         <v>110.53</v>
       </c>
-      <c r="F125" s="31">
+      <c r="F125" s="29">
         <v>66.5</v>
       </c>
-      <c r="G125" s="31" t="s">
+      <c r="G125" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="I125" s="29"/>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I125" s="1"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>69</v>
       </c>
@@ -15412,105 +15405,105 @@
       <c r="G126" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I126" s="29"/>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="41" t="s">
+      <c r="I126" s="1"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A127" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="B127" s="42">
+      <c r="B127" s="40">
         <v>45038</v>
       </c>
-      <c r="C127" s="31">
-        <v>0</v>
-      </c>
-      <c r="D127" s="31">
+      <c r="C127" s="29">
+        <v>0</v>
+      </c>
+      <c r="D127" s="29">
         <v>96.9</v>
       </c>
-      <c r="E127" s="31">
+      <c r="E127" s="29">
         <v>50.28</v>
       </c>
-      <c r="F127" s="31">
+      <c r="F127" s="29">
         <v>77.33</v>
       </c>
-      <c r="G127" s="31" t="s">
+      <c r="G127" s="29" t="s">
         <v>251</v>
       </c>
-      <c r="I127" s="29"/>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="41" t="s">
+      <c r="I127" s="1"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A128" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="B128" s="42">
+      <c r="B128" s="40">
         <v>45038</v>
       </c>
-      <c r="C128" s="31">
-        <v>0</v>
-      </c>
-      <c r="D128" s="31">
+      <c r="C128" s="29">
+        <v>0</v>
+      </c>
+      <c r="D128" s="29">
         <v>97</v>
       </c>
-      <c r="E128" s="31">
+      <c r="E128" s="29">
         <v>51.14</v>
       </c>
-      <c r="F128" s="31">
+      <c r="F128" s="29">
         <v>80.84</v>
       </c>
-      <c r="G128" s="31" t="s">
+      <c r="G128" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="I128" s="29"/>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="41" t="s">
+      <c r="I128" s="1"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A129" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="B129" s="42">
+      <c r="B129" s="40">
         <v>45038</v>
       </c>
-      <c r="C129" s="31">
-        <v>0</v>
-      </c>
-      <c r="D129" s="31">
+      <c r="C129" s="29">
+        <v>0</v>
+      </c>
+      <c r="D129" s="29">
         <v>97</v>
       </c>
-      <c r="E129" s="31">
+      <c r="E129" s="29">
         <v>52.12</v>
       </c>
-      <c r="F129" s="31">
+      <c r="F129" s="29">
         <v>81.61</v>
       </c>
-      <c r="G129" s="31" t="s">
+      <c r="G129" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="I129" s="29"/>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="41" t="s">
+      <c r="I129" s="1"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A130" s="39" t="s">
         <v>256</v>
       </c>
-      <c r="B130" s="42">
+      <c r="B130" s="40">
         <v>45038</v>
       </c>
-      <c r="C130" s="31">
-        <v>0</v>
-      </c>
-      <c r="D130" s="31">
+      <c r="C130" s="29">
+        <v>0</v>
+      </c>
+      <c r="D130" s="29">
         <v>97</v>
       </c>
-      <c r="E130" s="31">
+      <c r="E130" s="29">
         <v>53.19</v>
       </c>
-      <c r="F130" s="31">
+      <c r="F130" s="29">
         <v>83.9</v>
       </c>
-      <c r="G130" s="31" t="s">
+      <c r="G130" s="29" t="s">
         <v>257</v>
       </c>
-      <c r="I130" s="29"/>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I130" s="1"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="10" t="s">
         <v>123</v>
       </c>
@@ -15532,105 +15525,105 @@
       <c r="G131" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I131" s="29"/>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="41" t="s">
+      <c r="I131" s="1"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A132" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B132" s="42">
+      <c r="B132" s="40">
         <v>45039</v>
       </c>
-      <c r="C132" s="31">
-        <v>0</v>
-      </c>
-      <c r="D132" s="31">
+      <c r="C132" s="29">
+        <v>0</v>
+      </c>
+      <c r="D132" s="29">
         <v>95.4</v>
       </c>
-      <c r="E132" s="31">
+      <c r="E132" s="29">
         <v>65.36</v>
       </c>
-      <c r="F132" s="31">
+      <c r="F132" s="29">
         <v>59.88</v>
       </c>
-      <c r="G132" s="31" t="s">
+      <c r="G132" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="I132" s="29"/>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="41" t="s">
+      <c r="I132" s="1"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A133" s="39" t="s">
         <v>259</v>
       </c>
-      <c r="B133" s="42">
+      <c r="B133" s="40">
         <v>45039</v>
       </c>
-      <c r="C133" s="31">
-        <v>0</v>
-      </c>
-      <c r="D133" s="31">
+      <c r="C133" s="29">
+        <v>0</v>
+      </c>
+      <c r="D133" s="29">
         <v>95.4</v>
       </c>
-      <c r="E133" s="31">
+      <c r="E133" s="29">
         <v>67.44</v>
       </c>
-      <c r="F133" s="31">
+      <c r="F133" s="29">
         <v>61.6</v>
       </c>
-      <c r="G133" s="31" t="s">
+      <c r="G133" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="I133" s="29"/>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="41" t="s">
+      <c r="I133" s="1"/>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A134" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="B134" s="42">
+      <c r="B134" s="40">
         <v>45039</v>
       </c>
-      <c r="C134" s="31">
-        <v>0</v>
-      </c>
-      <c r="D134" s="31">
+      <c r="C134" s="29">
+        <v>0</v>
+      </c>
+      <c r="D134" s="29">
         <v>95.4</v>
       </c>
-      <c r="E134" s="31">
+      <c r="E134" s="29">
         <v>59.92</v>
       </c>
-      <c r="F134" s="31">
+      <c r="F134" s="29">
         <v>57.37</v>
       </c>
-      <c r="G134" s="31" t="s">
+      <c r="G134" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="I134" s="29"/>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="41" t="s">
+      <c r="I134" s="1"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A135" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="B135" s="42">
+      <c r="B135" s="40">
         <v>45039</v>
       </c>
-      <c r="C135" s="31">
-        <v>0</v>
-      </c>
-      <c r="D135" s="31">
+      <c r="C135" s="29">
+        <v>0</v>
+      </c>
+      <c r="D135" s="29">
         <v>95.3</v>
       </c>
-      <c r="E135" s="31">
+      <c r="E135" s="29">
         <v>61.42</v>
       </c>
-      <c r="F135" s="31">
+      <c r="F135" s="29">
         <v>57.97</v>
       </c>
-      <c r="G135" s="31" t="s">
+      <c r="G135" s="29" t="s">
         <v>264</v>
       </c>
-      <c r="I135" s="29"/>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I135" s="1"/>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="10" t="s">
         <v>133</v>
       </c>
@@ -15652,9 +15645,9 @@
       <c r="G136" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I136" s="29"/>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I136" s="1"/>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>156</v>
       </c>
@@ -15676,9 +15669,9 @@
       <c r="G137" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I137" s="29"/>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I137" s="1"/>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="12" t="s">
         <v>265</v>
       </c>
@@ -15700,273 +15693,273 @@
       <c r="G138" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I138" s="29"/>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="43" t="s">
+      <c r="I138" s="1"/>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A139" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="B139" s="44">
+      <c r="B139" s="42">
         <v>45034</v>
       </c>
-      <c r="C139" s="31">
-        <v>0</v>
-      </c>
-      <c r="D139" s="31">
+      <c r="C139" s="29">
+        <v>0</v>
+      </c>
+      <c r="D139" s="29">
         <v>95.6</v>
       </c>
-      <c r="E139" s="31">
+      <c r="E139" s="29">
         <v>49.93</v>
       </c>
-      <c r="F139" s="31">
+      <c r="F139" s="29">
         <v>64.2</v>
       </c>
-      <c r="G139" s="31" t="s">
+      <c r="G139" s="29" t="s">
         <v>266</v>
       </c>
-      <c r="I139" s="29"/>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="31" t="s">
+      <c r="I139" s="1"/>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A140" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="B140" s="44">
+      <c r="B140" s="42">
         <v>45034</v>
       </c>
-      <c r="C140" s="31">
-        <v>0</v>
-      </c>
-      <c r="D140" s="31">
+      <c r="C140" s="29">
+        <v>0</v>
+      </c>
+      <c r="D140" s="29">
         <v>95.5</v>
       </c>
-      <c r="E140" s="31">
+      <c r="E140" s="29">
         <v>52.93</v>
       </c>
-      <c r="F140" s="31">
+      <c r="F140" s="29">
         <v>65.03</v>
       </c>
-      <c r="G140" s="31" t="s">
+      <c r="G140" s="29" t="s">
         <v>268</v>
       </c>
-      <c r="I140" s="29"/>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="31" t="s">
+      <c r="I140" s="1"/>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A141" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="B141" s="38">
+      <c r="B141" s="36">
         <v>45034</v>
       </c>
-      <c r="C141" s="31">
-        <v>0</v>
-      </c>
-      <c r="D141" s="31">
+      <c r="C141" s="29">
+        <v>0</v>
+      </c>
+      <c r="D141" s="29">
         <v>95.6</v>
       </c>
-      <c r="E141" s="31">
+      <c r="E141" s="29">
         <v>55.66</v>
       </c>
-      <c r="F141" s="31">
+      <c r="F141" s="29">
         <v>66.680000000000007</v>
       </c>
-      <c r="G141" s="31" t="s">
+      <c r="G141" s="29" t="s">
         <v>270</v>
       </c>
-      <c r="I141" s="29"/>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="45" t="s">
+      <c r="I141" s="1"/>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A142" s="43" t="s">
         <v>271</v>
       </c>
-      <c r="B142" s="46">
+      <c r="B142" s="44">
         <v>45034</v>
       </c>
-      <c r="C142" s="31">
-        <v>0</v>
-      </c>
-      <c r="D142" s="31">
+      <c r="C142" s="29">
+        <v>0</v>
+      </c>
+      <c r="D142" s="29">
         <v>95.5</v>
       </c>
-      <c r="E142" s="31">
+      <c r="E142" s="29">
         <v>56.62</v>
       </c>
-      <c r="F142" s="31">
+      <c r="F142" s="29">
         <v>68.64</v>
       </c>
-      <c r="G142" s="31" t="s">
+      <c r="G142" s="29" t="s">
         <v>272</v>
       </c>
-      <c r="I142" s="29"/>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="45" t="s">
+      <c r="I142" s="1"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A143" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="B143" s="46">
+      <c r="B143" s="44">
         <v>45033</v>
       </c>
-      <c r="C143" s="31">
-        <v>0</v>
-      </c>
-      <c r="D143" s="31">
+      <c r="C143" s="29">
+        <v>0</v>
+      </c>
+      <c r="D143" s="29">
         <v>94.4</v>
       </c>
-      <c r="E143" s="31">
+      <c r="E143" s="29">
         <v>65.48</v>
       </c>
-      <c r="F143" s="31">
+      <c r="F143" s="29">
         <v>51.72</v>
       </c>
-      <c r="G143" s="31" t="s">
+      <c r="G143" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="I143" s="29"/>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="45" t="s">
+      <c r="I143" s="1"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A144" s="43" t="s">
         <v>274</v>
       </c>
-      <c r="B144" s="46">
+      <c r="B144" s="44">
         <v>45033</v>
       </c>
-      <c r="C144" s="31">
-        <v>0</v>
-      </c>
-      <c r="D144" s="31">
+      <c r="C144" s="29">
+        <v>0</v>
+      </c>
+      <c r="D144" s="29">
         <v>94</v>
       </c>
-      <c r="E144" s="31">
+      <c r="E144" s="29">
         <v>75.86</v>
       </c>
-      <c r="F144" s="31">
+      <c r="F144" s="29">
         <v>57.19</v>
       </c>
-      <c r="G144" s="31" t="s">
+      <c r="G144" s="29" t="s">
         <v>275</v>
       </c>
-      <c r="I144" s="29"/>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="45" t="s">
+      <c r="I144" s="1"/>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A145" s="43" t="s">
         <v>276</v>
       </c>
-      <c r="B145" s="46">
+      <c r="B145" s="44">
         <v>45033</v>
       </c>
-      <c r="C145" s="31">
-        <v>0</v>
-      </c>
-      <c r="D145" s="31">
+      <c r="C145" s="29">
+        <v>0</v>
+      </c>
+      <c r="D145" s="29">
         <v>94.2</v>
       </c>
-      <c r="E145" s="31">
+      <c r="E145" s="29">
         <v>94.2</v>
       </c>
-      <c r="F145" s="31">
+      <c r="F145" s="29">
         <v>68.83</v>
       </c>
-      <c r="G145" s="31" t="s">
+      <c r="G145" s="29" t="s">
         <v>277</v>
       </c>
-      <c r="I145" s="29"/>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="45" t="s">
+      <c r="I145" s="1"/>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A146" s="43" t="s">
         <v>278</v>
       </c>
-      <c r="B146" s="46">
+      <c r="B146" s="44">
         <v>45033</v>
       </c>
-      <c r="C146" s="31">
-        <v>0</v>
-      </c>
-      <c r="D146" s="31">
+      <c r="C146" s="29">
+        <v>0</v>
+      </c>
+      <c r="D146" s="29">
         <v>93.9</v>
       </c>
-      <c r="E146" s="31">
+      <c r="E146" s="29">
         <v>82.58</v>
       </c>
-      <c r="F146" s="31">
+      <c r="F146" s="29">
         <v>58.91</v>
       </c>
-      <c r="G146" s="31" t="s">
+      <c r="G146" s="29" t="s">
         <v>279</v>
       </c>
-      <c r="I146" s="29"/>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="45" t="s">
+      <c r="I146" s="1"/>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A147" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="B147" s="46">
+      <c r="B147" s="44">
         <v>45040</v>
       </c>
-      <c r="C147" s="31">
-        <v>0</v>
-      </c>
-      <c r="D147" s="31">
+      <c r="C147" s="29">
+        <v>0</v>
+      </c>
+      <c r="D147" s="29">
         <v>96.6</v>
       </c>
-      <c r="E147" s="31">
+      <c r="E147" s="29">
         <v>42.51</v>
       </c>
-      <c r="F147" s="31">
+      <c r="F147" s="29">
         <v>55.18</v>
       </c>
-      <c r="G147" s="31" t="s">
+      <c r="G147" s="29" t="s">
         <v>280</v>
       </c>
-      <c r="I147" s="29"/>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="45" t="s">
+      <c r="I147" s="1"/>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A148" s="43" t="s">
         <v>281</v>
       </c>
-      <c r="B148" s="46">
+      <c r="B148" s="44">
         <v>45040</v>
       </c>
-      <c r="C148" s="31">
-        <v>0</v>
-      </c>
-      <c r="D148" s="31">
+      <c r="C148" s="29">
+        <v>0</v>
+      </c>
+      <c r="D148" s="29">
         <v>96.5</v>
       </c>
-      <c r="E148" s="31">
+      <c r="E148" s="29">
         <v>49.12</v>
       </c>
-      <c r="F148" s="31">
+      <c r="F148" s="29">
         <v>61.13</v>
       </c>
-      <c r="G148" s="31" t="s">
+      <c r="G148" s="29" t="s">
         <v>282</v>
       </c>
-      <c r="I148" s="29"/>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="45" t="s">
+      <c r="I148" s="1"/>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A149" s="43" t="s">
         <v>283</v>
       </c>
-      <c r="B149" s="46">
+      <c r="B149" s="44">
         <v>45040</v>
       </c>
-      <c r="C149" s="31">
-        <v>0</v>
-      </c>
-      <c r="D149" s="31">
+      <c r="C149" s="29">
+        <v>0</v>
+      </c>
+      <c r="D149" s="29">
         <v>96.5</v>
       </c>
-      <c r="E149" s="31">
+      <c r="E149" s="29">
         <v>48.62</v>
       </c>
-      <c r="F149" s="31">
+      <c r="F149" s="29">
         <v>61.09</v>
       </c>
-      <c r="G149" s="31" t="s">
+      <c r="G149" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="I149" s="29"/>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I149" s="1"/>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="14" t="s">
         <v>10</v>
       </c>
@@ -15988,81 +15981,81 @@
       <c r="G150" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I150" s="29"/>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="45" t="s">
+      <c r="I150" s="1"/>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A151" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="B151" s="46">
+      <c r="B151" s="44">
         <v>45038</v>
       </c>
-      <c r="C151" s="31">
-        <v>0</v>
-      </c>
-      <c r="D151" s="31">
+      <c r="C151" s="29">
+        <v>0</v>
+      </c>
+      <c r="D151" s="29">
         <v>96.4</v>
       </c>
-      <c r="E151" s="31">
+      <c r="E151" s="29">
         <v>55.45</v>
       </c>
-      <c r="F151" s="31">
+      <c r="F151" s="29">
         <v>63.54</v>
       </c>
-      <c r="G151" s="31" t="s">
+      <c r="G151" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="I151" s="29"/>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="45" t="s">
+      <c r="I151" s="1"/>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A152" s="43" t="s">
         <v>286</v>
       </c>
-      <c r="B152" s="46">
+      <c r="B152" s="44">
         <v>45038</v>
       </c>
-      <c r="C152" s="31">
-        <v>0</v>
-      </c>
-      <c r="D152" s="31">
+      <c r="C152" s="29">
+        <v>0</v>
+      </c>
+      <c r="D152" s="29">
         <v>96.3</v>
       </c>
-      <c r="E152" s="31">
+      <c r="E152" s="29">
         <v>58.69</v>
       </c>
-      <c r="F152" s="31">
+      <c r="F152" s="29">
         <v>65.97</v>
       </c>
-      <c r="G152" s="31" t="s">
+      <c r="G152" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="I152" s="29"/>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="45" t="s">
+      <c r="I152" s="1"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A153" s="43" t="s">
         <v>288</v>
       </c>
-      <c r="B153" s="46">
+      <c r="B153" s="44">
         <v>45038</v>
       </c>
-      <c r="C153" s="31">
-        <v>0</v>
-      </c>
-      <c r="D153" s="31">
+      <c r="C153" s="29">
+        <v>0</v>
+      </c>
+      <c r="D153" s="29">
         <v>96.3</v>
       </c>
-      <c r="E153" s="31">
+      <c r="E153" s="29">
         <v>58.54</v>
       </c>
-      <c r="F153" s="31">
+      <c r="F153" s="29">
         <v>65.569999999999993</v>
       </c>
-      <c r="G153" s="31" t="s">
+      <c r="G153" s="29" t="s">
         <v>289</v>
       </c>
-      <c r="I153" s="29"/>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I153" s="1"/>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>113</v>
       </c>
@@ -16084,55 +16077,55 @@
       <c r="G154" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I154" s="29"/>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="43" t="s">
+      <c r="I154" s="1"/>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A155" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="B155" s="44">
+      <c r="B155" s="42">
         <v>45037</v>
       </c>
-      <c r="C155" s="31">
-        <v>0</v>
-      </c>
-      <c r="D155" s="31">
+      <c r="C155" s="29">
+        <v>0</v>
+      </c>
+      <c r="D155" s="29">
         <v>96</v>
       </c>
-      <c r="E155" s="31">
+      <c r="E155" s="29">
         <v>63.73</v>
       </c>
-      <c r="F155" s="31">
+      <c r="F155" s="29">
         <v>73.72</v>
       </c>
-      <c r="G155" s="31" t="s">
+      <c r="G155" s="29" t="s">
         <v>290</v>
       </c>
-      <c r="I155" s="29"/>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="43" t="s">
+      <c r="I155" s="1"/>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A156" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="B156" s="44">
+      <c r="B156" s="42">
         <v>45037</v>
       </c>
-      <c r="C156" s="31">
-        <v>0</v>
-      </c>
-      <c r="D156" s="31">
+      <c r="C156" s="29">
+        <v>0</v>
+      </c>
+      <c r="D156" s="29">
         <v>95.7</v>
       </c>
-      <c r="E156" s="31">
+      <c r="E156" s="29">
         <v>70.52</v>
       </c>
-      <c r="F156" s="31">
+      <c r="F156" s="29">
         <v>77.88</v>
       </c>
-      <c r="G156" s="31" t="s">
+      <c r="G156" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="I156" s="29"/>
+      <c r="I156" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="J3:O87" xr:uid="{47770336-139B-4E1D-B90D-A41F00945441}">
@@ -16154,29 +16147,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88255058-D6B0-44FE-B10F-105F557C8ECC}">
-  <dimension ref="A2:K28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="57"/>
+      <c r="B2" s="56"/>
       <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>2</v>
+      <c r="E2" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>4</v>
@@ -16184,551 +16178,551 @@
       <c r="G2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="28" t="s">
         <v>447</v>
       </c>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="28" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="29" t="s">
         <v>292</v>
       </c>
-      <c r="B3" s="32">
+      <c r="B3" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C3" s="31">
-        <v>0</v>
-      </c>
-      <c r="D3" s="31">
+      <c r="C3" s="29">
+        <v>0</v>
+      </c>
+      <c r="D3" s="29">
         <v>93.8</v>
       </c>
-      <c r="E3" s="31">
+      <c r="E3" s="29">
         <v>101.4</v>
       </c>
-      <c r="F3" s="31">
+      <c r="F3" s="29">
         <v>72.260000000000005</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="29" t="s">
         <v>293</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="I3" s="31" t="s">
         <v>292</v>
       </c>
-      <c r="J3" s="33">
+      <c r="J3" s="31">
         <v>106.28000000000002</v>
       </c>
-      <c r="K3" s="33">
+      <c r="K3" s="31">
         <v>74.303333333333342</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="29" t="s">
         <v>294</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C4" s="31">
-        <v>0</v>
-      </c>
-      <c r="D4" s="31">
+      <c r="C4" s="29">
+        <v>0</v>
+      </c>
+      <c r="D4" s="29">
         <v>93.7</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="29">
         <v>108.2</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="29">
         <v>74.290000000000006</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="31">
         <v>115.20499999999998</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="31">
         <v>62.445</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C5" s="31">
-        <v>0</v>
-      </c>
-      <c r="D5" s="31">
+      <c r="C5" s="29">
+        <v>0</v>
+      </c>
+      <c r="D5" s="29">
         <v>93.7</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="29">
         <v>109.24</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="29">
         <v>76.36</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="I5" s="33" t="s">
+      <c r="I5" s="31" t="s">
         <v>306</v>
       </c>
-      <c r="J5" s="33">
+      <c r="J5" s="31">
         <v>118.6825</v>
       </c>
-      <c r="K5" s="33">
+      <c r="K5" s="31">
         <v>78.204999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C6" s="31">
-        <v>0</v>
-      </c>
-      <c r="D6" s="31">
+      <c r="C6" s="29">
+        <v>0</v>
+      </c>
+      <c r="D6" s="29">
         <v>92.2</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="29">
         <v>112.57</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="29">
         <v>62.99</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="I6" s="33" t="s">
+      <c r="I6" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="J6" s="33">
+      <c r="J6" s="31">
         <v>73.134999999999991</v>
       </c>
-      <c r="K6" s="33">
+      <c r="K6" s="31">
         <v>62.120000000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C7" s="31">
-        <v>0</v>
-      </c>
-      <c r="D7" s="31">
+      <c r="C7" s="29">
+        <v>0</v>
+      </c>
+      <c r="D7" s="29">
         <v>91.9</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="29">
         <v>113.62</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="29">
         <v>61.82</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="29" t="s">
         <v>303</v>
       </c>
-      <c r="I7" s="33" t="s">
+      <c r="I7" s="31" t="s">
         <v>448</v>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="31">
         <v>110.62</v>
       </c>
-      <c r="K7" s="33">
+      <c r="K7" s="31">
         <v>77.547499999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="29" t="s">
         <v>301</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C8" s="31">
-        <v>0</v>
-      </c>
-      <c r="D8" s="31">
+      <c r="C8" s="29">
+        <v>0</v>
+      </c>
+      <c r="D8" s="29">
         <v>91.8</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="29">
         <v>116.35</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="29">
         <v>62.19</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="I8" s="33" t="s">
+      <c r="I8" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="31">
         <v>109.985</v>
       </c>
-      <c r="K8" s="33">
+      <c r="K8" s="31">
         <v>67.069999999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="29" t="s">
         <v>304</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C9" s="31">
-        <v>0</v>
-      </c>
-      <c r="D9" s="31">
+      <c r="C9" s="29">
+        <v>0</v>
+      </c>
+      <c r="D9" s="29">
         <v>91.7</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="29">
         <v>118.28</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="29">
         <v>62.78</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="29" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="29" t="s">
         <v>306</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C10" s="31">
-        <v>0</v>
-      </c>
-      <c r="D10" s="31">
+      <c r="C10" s="29">
+        <v>0</v>
+      </c>
+      <c r="D10" s="29">
         <v>92.8</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="29">
         <v>114.76</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="29">
         <v>81.010000000000005</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="29" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C11" s="31">
-        <v>0</v>
-      </c>
-      <c r="D11" s="31">
+      <c r="C11" s="29">
+        <v>0</v>
+      </c>
+      <c r="D11" s="29">
         <v>92.6</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="29">
         <v>112.26</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="29">
         <v>75.06</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="29" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="29" t="s">
         <v>310</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C12" s="31">
-        <v>0</v>
-      </c>
-      <c r="D12" s="31">
+      <c r="C12" s="29">
+        <v>0</v>
+      </c>
+      <c r="D12" s="29">
         <v>92.6</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="29">
         <v>123.07</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="29">
         <v>80.55</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="29" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="29" t="s">
         <v>312</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C13" s="31">
-        <v>0</v>
-      </c>
-      <c r="D13" s="31">
+      <c r="C13" s="29">
+        <v>0</v>
+      </c>
+      <c r="D13" s="29">
         <v>92.1</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="29">
         <v>124.64</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="29">
         <v>76.2</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="29" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="29" t="s">
         <v>314</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C14" s="31">
-        <v>0</v>
-      </c>
-      <c r="D14" s="31">
+      <c r="C14" s="29">
+        <v>0</v>
+      </c>
+      <c r="D14" s="29">
         <v>94.4</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="29">
         <v>74.45</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="29">
         <v>64.95</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="G14" s="29" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C15" s="31">
-        <v>0</v>
-      </c>
-      <c r="D15" s="31">
+      <c r="C15" s="29">
+        <v>0</v>
+      </c>
+      <c r="D15" s="29">
         <v>94</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="29">
         <v>71.58</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="29">
         <v>58.94</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="29" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="29" t="s">
         <v>318</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C16" s="31">
-        <v>0</v>
-      </c>
-      <c r="D16" s="31">
+      <c r="C16" s="29">
+        <v>0</v>
+      </c>
+      <c r="D16" s="29">
         <v>93.9</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="29">
         <v>72.819999999999993</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="29">
         <v>61.23</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="29" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="29" t="s">
         <v>320</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="30">
         <v>45029.777777777781</v>
       </c>
-      <c r="C17" s="31">
-        <v>0</v>
-      </c>
-      <c r="D17" s="31">
+      <c r="C17" s="29">
+        <v>0</v>
+      </c>
+      <c r="D17" s="29">
         <v>94</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="29">
         <v>73.69</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="29">
         <v>63.36</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="29" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="30">
         <v>45033.729166666664</v>
       </c>
-      <c r="C18" s="31">
-        <v>0</v>
-      </c>
-      <c r="D18" s="31">
+      <c r="C18" s="29">
+        <v>0</v>
+      </c>
+      <c r="D18" s="29">
         <v>93.4</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="29">
         <v>102.45</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="29">
         <v>76.41</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="29" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="30">
         <v>45033.729166666664</v>
       </c>
-      <c r="C19" s="31">
-        <v>0</v>
-      </c>
-      <c r="D19" s="31">
+      <c r="C19" s="29">
+        <v>0</v>
+      </c>
+      <c r="D19" s="29">
         <v>93.1</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="29">
         <v>112.65</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="29">
         <v>79.67</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="29" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="29" t="s">
         <v>326</v>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="30">
         <v>45033.729166666664</v>
       </c>
-      <c r="C20" s="31">
-        <v>0</v>
-      </c>
-      <c r="D20" s="31">
+      <c r="C20" s="29">
+        <v>0</v>
+      </c>
+      <c r="D20" s="29">
         <v>92.9</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="29">
         <v>116.13</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="29">
         <v>78.94</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="G20" s="29" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="29" t="s">
         <v>328</v>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="30">
         <v>45033.729166666664</v>
       </c>
-      <c r="C21" s="31">
-        <v>0</v>
-      </c>
-      <c r="D21" s="31">
+      <c r="C21" s="29">
+        <v>0</v>
+      </c>
+      <c r="D21" s="29">
         <v>92.8</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="29">
         <v>111.25</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="29">
         <v>75.17</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="G21" s="29" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="31" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="29" t="s">
         <v>330</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="30">
         <v>45033.729166666664</v>
       </c>
-      <c r="C22" s="31">
-        <v>0</v>
-      </c>
-      <c r="D22" s="31">
+      <c r="C22" s="29">
+        <v>0</v>
+      </c>
+      <c r="D22" s="29">
         <v>93.6</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="29">
         <v>108.11</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="29">
         <v>67.930000000000007</v>
       </c>
-      <c r="G22" s="31" t="s">
+      <c r="G22" s="29" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="30">
         <v>45033.729166666664</v>
       </c>
-      <c r="C23" s="31">
-        <v>0</v>
-      </c>
-      <c r="D23" s="31">
+      <c r="C23" s="29">
+        <v>0</v>
+      </c>
+      <c r="D23" s="29">
         <v>93.1</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E23" s="29">
         <v>111.86</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="29">
         <v>66.209999999999994</v>
       </c>
-      <c r="G23" s="31" t="s">
+      <c r="G23" s="29" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" s="13"/>
       <c r="C24" s="2"/>
@@ -16737,7 +16731,7 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
       <c r="B25" s="13"/>
       <c r="C25" s="2"/>
@@ -16746,7 +16740,7 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="12"/>
       <c r="B26" s="13"/>
       <c r="C26" s="2"/>
@@ -16755,7 +16749,7 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="12"/>
       <c r="B27" s="13"/>
       <c r="C27" s="2"/>
@@ -16764,7 +16758,7 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="12"/>
       <c r="B28" s="13"/>
       <c r="C28" s="2"/>
